--- a/class_excel/decision-making-under-uncertainty.xlsx
+++ b/class_excel/decision-making-under-uncertainty.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuna\Documents\GitHub\DADS7102\class_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A41A53D-2A96-406F-926D-204C7AC5FF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E302939E-6BAB-4A63-A50A-343490242E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="805" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="805" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variability" sheetId="14" r:id="rId1"/>
@@ -203,8 +203,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="228">
   <si>
     <t>Inputs</t>
   </si>
@@ -499,7 +521,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -514,7 +536,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -529,7 +551,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -544,7 +566,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -559,7 +581,7 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="Tahoma"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -913,6 +935,42 @@
   </si>
   <si>
     <t>V^0.5</t>
+  </si>
+  <si>
+    <t>mu</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>P(D&lt;=70) = F(70;mu;sigma)</t>
+  </si>
+  <si>
+    <t>in-class exercise</t>
+  </si>
+  <si>
+    <t>in-class exercise 2</t>
+  </si>
+  <si>
+    <t>std of demand/week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demand/week </t>
+  </si>
+  <si>
+    <t xml:space="preserve">reorder point </t>
+  </si>
+  <si>
+    <t xml:space="preserve">service level </t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>dependent</t>
   </si>
 </sst>
 </file>
@@ -920,26 +978,26 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="0.000000"/>
-    <numFmt numFmtId="169" formatCode="0.00000"/>
+    <numFmt numFmtId="187" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="188" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="189" formatCode="0.000"/>
+    <numFmt numFmtId="190" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="191" formatCode="0.0000"/>
+    <numFmt numFmtId="192" formatCode="0.000000"/>
+    <numFmt numFmtId="193" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -947,14 +1005,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -967,7 +1025,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -980,13 +1038,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1001,12 +1059,19 @@
       <u/>
       <sz val="11"/>
       <color indexed="12"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1046,6 +1111,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1254,7 +1325,7 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="187" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1263,11 +1334,11 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2"/>
@@ -1281,7 +1352,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1316,18 +1387,18 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="190" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="191" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="191" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -1335,7 +1406,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1364,7 +1435,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1377,12 +1448,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="6" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="191" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1396,7 +1467,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - Accent1" xfId="2" builtinId="30"/>
@@ -1753,20 +1828,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0739A870-1A44-4015-97BD-4BB6762B51B9}">
   <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.45" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.4375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.4375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.125" customWidth="1"/>
+    <col min="5" max="5" width="10.875" customWidth="1"/>
+    <col min="6" max="6" width="17.4375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.125" customWidth="1"/>
+    <col min="8" max="8" width="11.125" customWidth="1"/>
+    <col min="9" max="9" width="17.4375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="7" t="s">
         <v>129</v>
       </c>
@@ -1777,7 +1852,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>131</v>
       </c>
@@ -1801,7 +1876,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1827,7 +1902,7 @@
         <v>9.8344960000000619</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1853,7 +1928,7 @@
         <v>41.139395999999834</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1879,7 +1954,7 @@
         <v>432.47361600000085</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1905,7 +1980,7 @@
         <v>103.75459600000043</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1931,7 +2006,7 @@
         <v>297.07969600000064</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1957,7 +2032,7 @@
         <v>103.14433600000041</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1983,7 +2058,7 @@
         <v>872.25715599999864</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>8</v>
       </c>
@@ -2009,7 +2084,7 @@
         <v>3665.5759359999979</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>9</v>
       </c>
@@ -2035,7 +2110,7 @@
         <v>1098.6573160000009</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>10</v>
       </c>
@@ -2061,7 +2136,7 @@
         <v>3.3708960000000467</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>123</v>
       </c>
@@ -2072,7 +2147,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16">
         <f>AVERAGE(B4:B13)</f>
         <v>100</v>
@@ -2086,7 +2161,7 @@
         <v>100.07399999999998</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>119</v>
       </c>
@@ -2097,7 +2172,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="48">
         <f>SUM(C4:C13)/9</f>
         <v>0</v>
@@ -2124,7 +2199,7 @@
         <v>736.36527111111434</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>120</v>
       </c>
@@ -2135,7 +2210,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="48">
         <f>SUM(C4:C13)/10</f>
         <v>0</v>
@@ -2162,7 +2237,7 @@
         <v>662.72874400000433</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>124</v>
       </c>
@@ -2173,7 +2248,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="48">
         <f>SQRT(B19)</f>
         <v>0</v>
@@ -2200,7 +2275,7 @@
         <v>27.136051133337627</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>121</v>
       </c>
@@ -2211,7 +2286,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="48">
         <f>SQRT(B22)</f>
         <v>0</v>
@@ -2238,7 +2313,7 @@
         <v>25.743518485242152</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F29">
         <f>ROUNDUP(1.28*F28,0)</f>
         <v>4</v>
@@ -2256,15 +2331,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6C02113-42A9-47CB-BDB3-C9440B038F22}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.4375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2275,7 +2350,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2283,7 +2358,7 @@
         <v>6000000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2291,7 +2366,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2311,7 +2386,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2334,7 +2409,7 @@
         <v>0.61710711402488794</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2357,7 +2432,7 @@
         <v>-0.12749685157937574</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2380,7 +2455,7 @@
         <v>-1.4012753690986246</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -2388,7 +2463,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -2397,7 +2472,7 @@
         <v>-4.7180770561306817E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -2405,7 +2480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -2414,7 +2489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -2431,17 +2506,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD3D5A0-F96E-4065-ADE4-1E546597877D}">
   <dimension ref="A1:V9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
@@ -2479,7 +2554,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -2523,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -2571,7 +2646,7 @@
         <v>-118600</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -2625,7 +2700,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2679,7 +2754,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
         <v>41</v>
       </c>
@@ -2727,7 +2802,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -2784,7 +2859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -2845,7 +2920,7 @@
         <v>-6000</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -2871,20 +2946,20 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D37E63B8-EB9D-4227-BEBC-562734DDEEDE}">
   <dimension ref="A1:AH19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.5625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.5625" customWidth="1"/>
     <col min="14" max="31" width="5" customWidth="1"/>
     <col min="33" max="33" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B1" s="12" t="s">
         <v>37</v>
       </c>
@@ -2961,7 +3036,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -3059,7 +3134,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -3073,7 +3148,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -3150,7 +3225,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -3166,7 +3241,7 @@
       <c r="J5" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="K5" s="85">
+      <c r="K5" s="84">
         <v>0</v>
       </c>
       <c r="L5" s="41">
@@ -3175,7 +3250,7 @@
       <c r="M5" s="41">
         <v>0</v>
       </c>
-      <c r="N5" s="85">
+      <c r="N5" s="84">
         <v>0</v>
       </c>
       <c r="O5" s="41">
@@ -3190,10 +3265,10 @@
       <c r="R5" s="41">
         <v>0</v>
       </c>
-      <c r="S5" s="86">
-        <v>0</v>
-      </c>
-      <c r="T5" s="85">
+      <c r="S5" s="85">
+        <v>0</v>
+      </c>
+      <c r="T5" s="84">
         <v>0</v>
       </c>
       <c r="U5" s="41">
@@ -3208,10 +3283,10 @@
       <c r="X5" s="41">
         <v>0</v>
       </c>
-      <c r="Y5" s="86">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="85">
+      <c r="Y5" s="85">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="84">
         <v>0</v>
       </c>
       <c r="AA5" s="41">
@@ -3226,11 +3301,11 @@
       <c r="AD5" s="41">
         <v>0</v>
       </c>
-      <c r="AE5" s="86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AE5" s="85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D6" t="s">
         <v>41</v>
       </c>
@@ -3329,7 +3404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -3386,7 +3461,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -3463,7 +3538,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -3527,7 +3602,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="I10" s="89"/>
       <c r="J10" t="s">
         <v>62</v>
@@ -3576,7 +3651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
       <c r="I11" s="90"/>
       <c r="J11" s="26" t="s">
         <v>63</v>
@@ -3631,7 +3706,7 @@
         <v>-6000</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="I12" s="91" t="s">
         <v>85</v>
       </c>
@@ -3688,7 +3763,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
       <c r="I13" s="89"/>
       <c r="J13" t="s">
         <v>38</v>
@@ -3735,7 +3810,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="I14" s="89"/>
       <c r="J14" t="s">
         <v>62</v>
@@ -3782,7 +3857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="I15" s="90"/>
       <c r="J15" s="26" t="s">
         <v>63</v>
@@ -3837,7 +3912,7 @@
         <v>-6000</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
       <c r="I16" s="91" t="s">
         <v>88</v>
       </c>
@@ -3895,7 +3970,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="9:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="9:34" x14ac:dyDescent="0.35">
       <c r="I17" s="89"/>
       <c r="J17" t="s">
         <v>38</v>
@@ -3943,7 +4018,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="18" spans="9:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="9:34" x14ac:dyDescent="0.35">
       <c r="I18" s="89"/>
       <c r="J18" t="s">
         <v>62</v>
@@ -3991,7 +4066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="9:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="9:34" x14ac:dyDescent="0.35">
       <c r="I19" s="90"/>
       <c r="J19" s="26" t="s">
         <v>63</v>
@@ -4059,14 +4134,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56305144-AAEF-43EC-981E-EB9116AF8342}">
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>107</v>
       </c>
@@ -4080,7 +4155,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>105</v>
       </c>
@@ -4097,7 +4172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>106</v>
       </c>
@@ -4118,7 +4193,7 @@
         <v>-8819.6577446248266</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>111</v>
       </c>
@@ -4145,7 +4220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>112</v>
       </c>
@@ -4172,7 +4247,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>113</v>
       </c>
@@ -4199,7 +4274,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>114</v>
       </c>
@@ -4226,7 +4301,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>115</v>
       </c>
@@ -4261,15 +4336,15 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9329BF31-CF05-4B51-94D8-0713A85BA077}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>117</v>
       </c>
@@ -4286,7 +4361,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>104</v>
       </c>
@@ -4303,7 +4378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B3">
         <f>B2*B6</f>
         <v>4.1029374284684013E-2</v>
@@ -4321,7 +4396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>107</v>
       </c>
@@ -4335,7 +4410,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>105</v>
       </c>
@@ -4352,7 +4427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>106</v>
       </c>
@@ -4374,7 +4449,7 @@
       </c>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -4401,7 +4476,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -4428,7 +4503,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>114</v>
       </c>
@@ -4455,7 +4530,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>115</v>
       </c>
@@ -4482,7 +4557,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>118</v>
       </c>
@@ -4505,16 +4580,16 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E936C5E6-48EB-470A-826D-E40B341C7C76}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.5703125" customWidth="1"/>
-    <col min="8" max="8" width="7.85546875" customWidth="1"/>
+    <col min="1" max="1" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.4375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.5625" customWidth="1"/>
+    <col min="8" max="8" width="7.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>180</v>
       </c>
@@ -4540,7 +4615,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4569,7 +4644,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4598,7 +4673,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4627,7 +4702,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4657,7 +4732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4680,7 +4755,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4704,7 +4779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4721,7 +4796,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4738,7 +4813,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4755,7 +4830,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4772,7 +4847,7 @@
         <v>0.10200000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4789,7 +4864,7 @@
         <v>1.6500000000000001E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4806,7 +4881,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4823,7 +4898,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4840,7 +4915,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4857,7 +4932,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>179</v>
       </c>
@@ -4873,14 +4948,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC0FD636-D113-430E-8AEF-CC8AB78B6538}">
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.125" customWidth="1"/>
+    <col min="2" max="2" width="10.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="13.9" x14ac:dyDescent="0.4">
       <c r="A1" s="49" t="s">
         <v>132</v>
       </c>
@@ -4889,23 +4964,23 @@
         <v>0.73401447095129946</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="F2">
         <f>_xlfn.NORM.INV(0.9, 1085, 164)</f>
         <v>1295.1744567493145</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="13.9" x14ac:dyDescent="0.4">
       <c r="A3" s="49" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="13.9" x14ac:dyDescent="0.4">
       <c r="A5" s="49" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>135</v>
       </c>
@@ -4916,80 +4991,86 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>137</v>
       </c>
       <c r="B7" s="48"/>
       <c r="D7" s="50"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>138</v>
       </c>
       <c r="B8" s="48"/>
       <c r="D8" s="50"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>139</v>
       </c>
       <c r="B9" s="48"/>
       <c r="D9" s="50"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="13.9" x14ac:dyDescent="0.4">
       <c r="A11" s="49" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>141</v>
       </c>
       <c r="B12" s="3"/>
       <c r="D12" s="51"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>142</v>
       </c>
       <c r="B13" s="3"/>
       <c r="D13" s="51"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>143</v>
       </c>
       <c r="B14" s="3"/>
       <c r="D14" s="51"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="13.9" x14ac:dyDescent="0.4">
       <c r="A16" s="49" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>123</v>
       </c>
       <c r="B18" s="52">
         <v>75</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C18" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>145</v>
       </c>
       <c r="B19" s="52">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="13.9" x14ac:dyDescent="0.4">
       <c r="A21" s="49" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>135</v>
       </c>
@@ -5000,52 +5081,123 @@
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>146</v>
       </c>
-      <c r="B23" s="48"/>
+      <c r="B23" s="48">
+        <f>_xlfn.NORM.DIST(80,$B$18,$B$19,TRUE)</f>
+        <v>0.73401447095129946</v>
+      </c>
       <c r="D23" s="53"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>147</v>
       </c>
       <c r="B24" s="48"/>
       <c r="D24" s="53"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>148</v>
       </c>
       <c r="B25" s="48"/>
       <c r="D25" s="53"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="13.9" x14ac:dyDescent="0.4">
       <c r="A27" s="49" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>141</v>
       </c>
       <c r="B28" s="3"/>
       <c r="D28" s="51"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>149</v>
       </c>
       <c r="B29" s="3"/>
       <c r="D29" s="51"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>150</v>
       </c>
-      <c r="B30" s="3"/>
+      <c r="B30" s="3">
+        <f>_xlfn.NORM.INV(0.97,$B$18,$B$19)</f>
+        <v>90.046348865210007</v>
+      </c>
       <c r="D30" s="51"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>219</v>
+      </c>
+      <c r="B31">
+        <f>_xlfn.NORM.INV(0.9, 1085, 164)</f>
+        <v>1295.1744567493145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>222</v>
+      </c>
+      <c r="B36">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>221</v>
+      </c>
+      <c r="B37">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>223</v>
+      </c>
+      <c r="B38">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" s="41">
+        <f>_xlfn.NORM.DIST(B38,B36,B37, TRUE)</f>
+        <v>0.79767161903635697</v>
+      </c>
+      <c r="C39" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39">
+        <v>0.97499999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C40" t="s">
+        <v>225</v>
+      </c>
+      <c r="D40" s="8">
+        <f>_xlfn.NORM.INV(D39, B36,B37)</f>
+        <v>617.59783907240319</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5054,15 +5206,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BCB24F-2CC1-4024-8E71-BDF4D5BCC4E8}">
-  <dimension ref="A1:V14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V17"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.4375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.4375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="F1" t="s">
         <v>154</v>
       </c>
@@ -5070,7 +5223,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="13.9" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>151</v>
       </c>
@@ -5090,7 +5243,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>155</v>
       </c>
@@ -5127,7 +5280,7 @@
       <c r="P3" t="s">
         <v>208</v>
       </c>
-      <c r="S3" s="92" t="s">
+      <c r="S3" s="86" t="s">
         <v>205</v>
       </c>
       <c r="T3" t="s">
@@ -5140,7 +5293,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>156</v>
       </c>
@@ -5191,7 +5344,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="F5" t="s">
         <v>153</v>
       </c>
@@ -5231,7 +5384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="M6" t="s">
         <v>210</v>
       </c>
@@ -5262,7 +5415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="L8" t="s">
         <v>211</v>
       </c>
@@ -5270,14 +5423,21 @@
         <f>SUM(N4:P4)</f>
         <v>38</v>
       </c>
-      <c r="S8" t="s">
+      <c r="S8" s="93" t="s">
         <v>214</v>
       </c>
-      <c r="T8" s="31"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="31"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T8" s="31" cm="1">
+        <f t="array" ref="T8:V10">MMULT(MMULT(N12:P14,T4:V6),N12:P14)</f>
+        <v>4</v>
+      </c>
+      <c r="U8" s="31">
+        <v>-3</v>
+      </c>
+      <c r="V8" s="31">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="L9" t="s">
         <v>212</v>
       </c>
@@ -5285,11 +5445,17 @@
         <f>SUM(N6:P6)</f>
         <v>29.25</v>
       </c>
-      <c r="T9" s="31"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="31"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T9" s="31">
+        <v>-3</v>
+      </c>
+      <c r="U9" s="31">
+        <v>25</v>
+      </c>
+      <c r="V9" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="L10" t="s">
         <v>213</v>
       </c>
@@ -5297,30 +5463,90 @@
         <f>SQRT(M9)</f>
         <v>5.4083269131959844</v>
       </c>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="31"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T10" s="31">
+        <v>0.1</v>
+      </c>
+      <c r="U10" s="31">
+        <v>0</v>
+      </c>
+      <c r="V10" s="31">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="L12" t="s">
         <v>215</v>
       </c>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="31"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="31">
+        <f>N5</f>
+        <v>2</v>
+      </c>
+      <c r="O12" s="31">
+        <v>0</v>
+      </c>
+      <c r="P12" s="31">
+        <v>0</v>
+      </c>
+      <c r="S12" t="s">
+        <v>226</v>
+      </c>
+      <c r="T12" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="M13" s="92"/>
+      <c r="N13" s="31">
+        <v>0</v>
+      </c>
+      <c r="O13" s="31">
+        <f>O5</f>
+        <v>5</v>
+      </c>
+      <c r="P13" s="31">
+        <v>0</v>
+      </c>
+      <c r="T13" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="M14" s="92"/>
+      <c r="N14" s="31">
+        <v>0</v>
+      </c>
+      <c r="O14" s="31">
+        <v>0</v>
+      </c>
+      <c r="P14" s="31">
+        <f>P5</f>
+        <v>0.5</v>
+      </c>
+      <c r="T14" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="R16" s="94" t="s">
+        <v>227</v>
+      </c>
+      <c r="S16" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="T16" cm="1">
+        <f t="array" ref="T16">MMULT(MMULT(TRANSPOSE(T12:T14),_xlfn.ANCHORARRAY(T8)),T12:T14)</f>
+        <v>23.450000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="19:20" x14ac:dyDescent="0.35">
+      <c r="S17" t="s">
+        <v>213</v>
+      </c>
+      <c r="T17">
+        <f>SQRT(T16)</f>
+        <v>4.8425200051213011</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5330,345 +5556,345 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36E6B8BC-DC12-44B6-8732-32E3ACF6FCD2}">
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" style="58" customWidth="1"/>
-    <col min="2" max="5" width="16.85546875" style="58" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" style="58" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="58" customWidth="1"/>
-    <col min="8" max="256" width="8.85546875" style="58"/>
-    <col min="257" max="257" width="21.85546875" style="58" customWidth="1"/>
-    <col min="258" max="261" width="16.85546875" style="58" customWidth="1"/>
-    <col min="262" max="262" width="17.85546875" style="58" customWidth="1"/>
-    <col min="263" max="263" width="11.5703125" style="58" customWidth="1"/>
-    <col min="264" max="512" width="8.85546875" style="58"/>
-    <col min="513" max="513" width="21.85546875" style="58" customWidth="1"/>
-    <col min="514" max="517" width="16.85546875" style="58" customWidth="1"/>
-    <col min="518" max="518" width="17.85546875" style="58" customWidth="1"/>
-    <col min="519" max="519" width="11.5703125" style="58" customWidth="1"/>
-    <col min="520" max="768" width="8.85546875" style="58"/>
-    <col min="769" max="769" width="21.85546875" style="58" customWidth="1"/>
-    <col min="770" max="773" width="16.85546875" style="58" customWidth="1"/>
-    <col min="774" max="774" width="17.85546875" style="58" customWidth="1"/>
-    <col min="775" max="775" width="11.5703125" style="58" customWidth="1"/>
-    <col min="776" max="1024" width="8.85546875" style="58"/>
-    <col min="1025" max="1025" width="21.85546875" style="58" customWidth="1"/>
-    <col min="1026" max="1029" width="16.85546875" style="58" customWidth="1"/>
-    <col min="1030" max="1030" width="17.85546875" style="58" customWidth="1"/>
-    <col min="1031" max="1031" width="11.5703125" style="58" customWidth="1"/>
-    <col min="1032" max="1280" width="8.85546875" style="58"/>
-    <col min="1281" max="1281" width="21.85546875" style="58" customWidth="1"/>
-    <col min="1282" max="1285" width="16.85546875" style="58" customWidth="1"/>
-    <col min="1286" max="1286" width="17.85546875" style="58" customWidth="1"/>
-    <col min="1287" max="1287" width="11.5703125" style="58" customWidth="1"/>
-    <col min="1288" max="1536" width="8.85546875" style="58"/>
-    <col min="1537" max="1537" width="21.85546875" style="58" customWidth="1"/>
-    <col min="1538" max="1541" width="16.85546875" style="58" customWidth="1"/>
-    <col min="1542" max="1542" width="17.85546875" style="58" customWidth="1"/>
-    <col min="1543" max="1543" width="11.5703125" style="58" customWidth="1"/>
-    <col min="1544" max="1792" width="8.85546875" style="58"/>
-    <col min="1793" max="1793" width="21.85546875" style="58" customWidth="1"/>
-    <col min="1794" max="1797" width="16.85546875" style="58" customWidth="1"/>
-    <col min="1798" max="1798" width="17.85546875" style="58" customWidth="1"/>
-    <col min="1799" max="1799" width="11.5703125" style="58" customWidth="1"/>
-    <col min="1800" max="2048" width="8.85546875" style="58"/>
-    <col min="2049" max="2049" width="21.85546875" style="58" customWidth="1"/>
-    <col min="2050" max="2053" width="16.85546875" style="58" customWidth="1"/>
-    <col min="2054" max="2054" width="17.85546875" style="58" customWidth="1"/>
-    <col min="2055" max="2055" width="11.5703125" style="58" customWidth="1"/>
-    <col min="2056" max="2304" width="8.85546875" style="58"/>
-    <col min="2305" max="2305" width="21.85546875" style="58" customWidth="1"/>
-    <col min="2306" max="2309" width="16.85546875" style="58" customWidth="1"/>
-    <col min="2310" max="2310" width="17.85546875" style="58" customWidth="1"/>
-    <col min="2311" max="2311" width="11.5703125" style="58" customWidth="1"/>
-    <col min="2312" max="2560" width="8.85546875" style="58"/>
-    <col min="2561" max="2561" width="21.85546875" style="58" customWidth="1"/>
-    <col min="2562" max="2565" width="16.85546875" style="58" customWidth="1"/>
-    <col min="2566" max="2566" width="17.85546875" style="58" customWidth="1"/>
-    <col min="2567" max="2567" width="11.5703125" style="58" customWidth="1"/>
-    <col min="2568" max="2816" width="8.85546875" style="58"/>
-    <col min="2817" max="2817" width="21.85546875" style="58" customWidth="1"/>
-    <col min="2818" max="2821" width="16.85546875" style="58" customWidth="1"/>
-    <col min="2822" max="2822" width="17.85546875" style="58" customWidth="1"/>
-    <col min="2823" max="2823" width="11.5703125" style="58" customWidth="1"/>
-    <col min="2824" max="3072" width="8.85546875" style="58"/>
-    <col min="3073" max="3073" width="21.85546875" style="58" customWidth="1"/>
-    <col min="3074" max="3077" width="16.85546875" style="58" customWidth="1"/>
-    <col min="3078" max="3078" width="17.85546875" style="58" customWidth="1"/>
-    <col min="3079" max="3079" width="11.5703125" style="58" customWidth="1"/>
-    <col min="3080" max="3328" width="8.85546875" style="58"/>
-    <col min="3329" max="3329" width="21.85546875" style="58" customWidth="1"/>
-    <col min="3330" max="3333" width="16.85546875" style="58" customWidth="1"/>
-    <col min="3334" max="3334" width="17.85546875" style="58" customWidth="1"/>
-    <col min="3335" max="3335" width="11.5703125" style="58" customWidth="1"/>
-    <col min="3336" max="3584" width="8.85546875" style="58"/>
-    <col min="3585" max="3585" width="21.85546875" style="58" customWidth="1"/>
-    <col min="3586" max="3589" width="16.85546875" style="58" customWidth="1"/>
-    <col min="3590" max="3590" width="17.85546875" style="58" customWidth="1"/>
-    <col min="3591" max="3591" width="11.5703125" style="58" customWidth="1"/>
-    <col min="3592" max="3840" width="8.85546875" style="58"/>
-    <col min="3841" max="3841" width="21.85546875" style="58" customWidth="1"/>
-    <col min="3842" max="3845" width="16.85546875" style="58" customWidth="1"/>
-    <col min="3846" max="3846" width="17.85546875" style="58" customWidth="1"/>
-    <col min="3847" max="3847" width="11.5703125" style="58" customWidth="1"/>
-    <col min="3848" max="4096" width="8.85546875" style="58"/>
-    <col min="4097" max="4097" width="21.85546875" style="58" customWidth="1"/>
-    <col min="4098" max="4101" width="16.85546875" style="58" customWidth="1"/>
-    <col min="4102" max="4102" width="17.85546875" style="58" customWidth="1"/>
-    <col min="4103" max="4103" width="11.5703125" style="58" customWidth="1"/>
-    <col min="4104" max="4352" width="8.85546875" style="58"/>
-    <col min="4353" max="4353" width="21.85546875" style="58" customWidth="1"/>
-    <col min="4354" max="4357" width="16.85546875" style="58" customWidth="1"/>
-    <col min="4358" max="4358" width="17.85546875" style="58" customWidth="1"/>
-    <col min="4359" max="4359" width="11.5703125" style="58" customWidth="1"/>
-    <col min="4360" max="4608" width="8.85546875" style="58"/>
-    <col min="4609" max="4609" width="21.85546875" style="58" customWidth="1"/>
-    <col min="4610" max="4613" width="16.85546875" style="58" customWidth="1"/>
-    <col min="4614" max="4614" width="17.85546875" style="58" customWidth="1"/>
-    <col min="4615" max="4615" width="11.5703125" style="58" customWidth="1"/>
-    <col min="4616" max="4864" width="8.85546875" style="58"/>
-    <col min="4865" max="4865" width="21.85546875" style="58" customWidth="1"/>
-    <col min="4866" max="4869" width="16.85546875" style="58" customWidth="1"/>
-    <col min="4870" max="4870" width="17.85546875" style="58" customWidth="1"/>
-    <col min="4871" max="4871" width="11.5703125" style="58" customWidth="1"/>
-    <col min="4872" max="5120" width="8.85546875" style="58"/>
-    <col min="5121" max="5121" width="21.85546875" style="58" customWidth="1"/>
-    <col min="5122" max="5125" width="16.85546875" style="58" customWidth="1"/>
-    <col min="5126" max="5126" width="17.85546875" style="58" customWidth="1"/>
-    <col min="5127" max="5127" width="11.5703125" style="58" customWidth="1"/>
-    <col min="5128" max="5376" width="8.85546875" style="58"/>
-    <col min="5377" max="5377" width="21.85546875" style="58" customWidth="1"/>
-    <col min="5378" max="5381" width="16.85546875" style="58" customWidth="1"/>
-    <col min="5382" max="5382" width="17.85546875" style="58" customWidth="1"/>
-    <col min="5383" max="5383" width="11.5703125" style="58" customWidth="1"/>
-    <col min="5384" max="5632" width="8.85546875" style="58"/>
-    <col min="5633" max="5633" width="21.85546875" style="58" customWidth="1"/>
-    <col min="5634" max="5637" width="16.85546875" style="58" customWidth="1"/>
-    <col min="5638" max="5638" width="17.85546875" style="58" customWidth="1"/>
-    <col min="5639" max="5639" width="11.5703125" style="58" customWidth="1"/>
-    <col min="5640" max="5888" width="8.85546875" style="58"/>
-    <col min="5889" max="5889" width="21.85546875" style="58" customWidth="1"/>
-    <col min="5890" max="5893" width="16.85546875" style="58" customWidth="1"/>
-    <col min="5894" max="5894" width="17.85546875" style="58" customWidth="1"/>
-    <col min="5895" max="5895" width="11.5703125" style="58" customWidth="1"/>
-    <col min="5896" max="6144" width="8.85546875" style="58"/>
-    <col min="6145" max="6145" width="21.85546875" style="58" customWidth="1"/>
-    <col min="6146" max="6149" width="16.85546875" style="58" customWidth="1"/>
-    <col min="6150" max="6150" width="17.85546875" style="58" customWidth="1"/>
-    <col min="6151" max="6151" width="11.5703125" style="58" customWidth="1"/>
-    <col min="6152" max="6400" width="8.85546875" style="58"/>
-    <col min="6401" max="6401" width="21.85546875" style="58" customWidth="1"/>
-    <col min="6402" max="6405" width="16.85546875" style="58" customWidth="1"/>
-    <col min="6406" max="6406" width="17.85546875" style="58" customWidth="1"/>
-    <col min="6407" max="6407" width="11.5703125" style="58" customWidth="1"/>
-    <col min="6408" max="6656" width="8.85546875" style="58"/>
-    <col min="6657" max="6657" width="21.85546875" style="58" customWidth="1"/>
-    <col min="6658" max="6661" width="16.85546875" style="58" customWidth="1"/>
-    <col min="6662" max="6662" width="17.85546875" style="58" customWidth="1"/>
-    <col min="6663" max="6663" width="11.5703125" style="58" customWidth="1"/>
-    <col min="6664" max="6912" width="8.85546875" style="58"/>
-    <col min="6913" max="6913" width="21.85546875" style="58" customWidth="1"/>
-    <col min="6914" max="6917" width="16.85546875" style="58" customWidth="1"/>
-    <col min="6918" max="6918" width="17.85546875" style="58" customWidth="1"/>
-    <col min="6919" max="6919" width="11.5703125" style="58" customWidth="1"/>
-    <col min="6920" max="7168" width="8.85546875" style="58"/>
-    <col min="7169" max="7169" width="21.85546875" style="58" customWidth="1"/>
-    <col min="7170" max="7173" width="16.85546875" style="58" customWidth="1"/>
-    <col min="7174" max="7174" width="17.85546875" style="58" customWidth="1"/>
-    <col min="7175" max="7175" width="11.5703125" style="58" customWidth="1"/>
-    <col min="7176" max="7424" width="8.85546875" style="58"/>
-    <col min="7425" max="7425" width="21.85546875" style="58" customWidth="1"/>
-    <col min="7426" max="7429" width="16.85546875" style="58" customWidth="1"/>
-    <col min="7430" max="7430" width="17.85546875" style="58" customWidth="1"/>
-    <col min="7431" max="7431" width="11.5703125" style="58" customWidth="1"/>
-    <col min="7432" max="7680" width="8.85546875" style="58"/>
-    <col min="7681" max="7681" width="21.85546875" style="58" customWidth="1"/>
-    <col min="7682" max="7685" width="16.85546875" style="58" customWidth="1"/>
-    <col min="7686" max="7686" width="17.85546875" style="58" customWidth="1"/>
-    <col min="7687" max="7687" width="11.5703125" style="58" customWidth="1"/>
-    <col min="7688" max="7936" width="8.85546875" style="58"/>
-    <col min="7937" max="7937" width="21.85546875" style="58" customWidth="1"/>
-    <col min="7938" max="7941" width="16.85546875" style="58" customWidth="1"/>
-    <col min="7942" max="7942" width="17.85546875" style="58" customWidth="1"/>
-    <col min="7943" max="7943" width="11.5703125" style="58" customWidth="1"/>
-    <col min="7944" max="8192" width="8.85546875" style="58"/>
-    <col min="8193" max="8193" width="21.85546875" style="58" customWidth="1"/>
-    <col min="8194" max="8197" width="16.85546875" style="58" customWidth="1"/>
-    <col min="8198" max="8198" width="17.85546875" style="58" customWidth="1"/>
-    <col min="8199" max="8199" width="11.5703125" style="58" customWidth="1"/>
-    <col min="8200" max="8448" width="8.85546875" style="58"/>
-    <col min="8449" max="8449" width="21.85546875" style="58" customWidth="1"/>
-    <col min="8450" max="8453" width="16.85546875" style="58" customWidth="1"/>
-    <col min="8454" max="8454" width="17.85546875" style="58" customWidth="1"/>
-    <col min="8455" max="8455" width="11.5703125" style="58" customWidth="1"/>
-    <col min="8456" max="8704" width="8.85546875" style="58"/>
-    <col min="8705" max="8705" width="21.85546875" style="58" customWidth="1"/>
-    <col min="8706" max="8709" width="16.85546875" style="58" customWidth="1"/>
-    <col min="8710" max="8710" width="17.85546875" style="58" customWidth="1"/>
-    <col min="8711" max="8711" width="11.5703125" style="58" customWidth="1"/>
-    <col min="8712" max="8960" width="8.85546875" style="58"/>
-    <col min="8961" max="8961" width="21.85546875" style="58" customWidth="1"/>
-    <col min="8962" max="8965" width="16.85546875" style="58" customWidth="1"/>
-    <col min="8966" max="8966" width="17.85546875" style="58" customWidth="1"/>
-    <col min="8967" max="8967" width="11.5703125" style="58" customWidth="1"/>
-    <col min="8968" max="9216" width="8.85546875" style="58"/>
-    <col min="9217" max="9217" width="21.85546875" style="58" customWidth="1"/>
-    <col min="9218" max="9221" width="16.85546875" style="58" customWidth="1"/>
-    <col min="9222" max="9222" width="17.85546875" style="58" customWidth="1"/>
-    <col min="9223" max="9223" width="11.5703125" style="58" customWidth="1"/>
-    <col min="9224" max="9472" width="8.85546875" style="58"/>
-    <col min="9473" max="9473" width="21.85546875" style="58" customWidth="1"/>
-    <col min="9474" max="9477" width="16.85546875" style="58" customWidth="1"/>
-    <col min="9478" max="9478" width="17.85546875" style="58" customWidth="1"/>
-    <col min="9479" max="9479" width="11.5703125" style="58" customWidth="1"/>
-    <col min="9480" max="9728" width="8.85546875" style="58"/>
-    <col min="9729" max="9729" width="21.85546875" style="58" customWidth="1"/>
-    <col min="9730" max="9733" width="16.85546875" style="58" customWidth="1"/>
-    <col min="9734" max="9734" width="17.85546875" style="58" customWidth="1"/>
-    <col min="9735" max="9735" width="11.5703125" style="58" customWidth="1"/>
-    <col min="9736" max="9984" width="8.85546875" style="58"/>
-    <col min="9985" max="9985" width="21.85546875" style="58" customWidth="1"/>
-    <col min="9986" max="9989" width="16.85546875" style="58" customWidth="1"/>
-    <col min="9990" max="9990" width="17.85546875" style="58" customWidth="1"/>
-    <col min="9991" max="9991" width="11.5703125" style="58" customWidth="1"/>
-    <col min="9992" max="10240" width="8.85546875" style="58"/>
-    <col min="10241" max="10241" width="21.85546875" style="58" customWidth="1"/>
-    <col min="10242" max="10245" width="16.85546875" style="58" customWidth="1"/>
-    <col min="10246" max="10246" width="17.85546875" style="58" customWidth="1"/>
-    <col min="10247" max="10247" width="11.5703125" style="58" customWidth="1"/>
-    <col min="10248" max="10496" width="8.85546875" style="58"/>
-    <col min="10497" max="10497" width="21.85546875" style="58" customWidth="1"/>
-    <col min="10498" max="10501" width="16.85546875" style="58" customWidth="1"/>
-    <col min="10502" max="10502" width="17.85546875" style="58" customWidth="1"/>
-    <col min="10503" max="10503" width="11.5703125" style="58" customWidth="1"/>
-    <col min="10504" max="10752" width="8.85546875" style="58"/>
-    <col min="10753" max="10753" width="21.85546875" style="58" customWidth="1"/>
-    <col min="10754" max="10757" width="16.85546875" style="58" customWidth="1"/>
-    <col min="10758" max="10758" width="17.85546875" style="58" customWidth="1"/>
-    <col min="10759" max="10759" width="11.5703125" style="58" customWidth="1"/>
-    <col min="10760" max="11008" width="8.85546875" style="58"/>
-    <col min="11009" max="11009" width="21.85546875" style="58" customWidth="1"/>
-    <col min="11010" max="11013" width="16.85546875" style="58" customWidth="1"/>
-    <col min="11014" max="11014" width="17.85546875" style="58" customWidth="1"/>
-    <col min="11015" max="11015" width="11.5703125" style="58" customWidth="1"/>
-    <col min="11016" max="11264" width="8.85546875" style="58"/>
-    <col min="11265" max="11265" width="21.85546875" style="58" customWidth="1"/>
-    <col min="11266" max="11269" width="16.85546875" style="58" customWidth="1"/>
-    <col min="11270" max="11270" width="17.85546875" style="58" customWidth="1"/>
-    <col min="11271" max="11271" width="11.5703125" style="58" customWidth="1"/>
-    <col min="11272" max="11520" width="8.85546875" style="58"/>
-    <col min="11521" max="11521" width="21.85546875" style="58" customWidth="1"/>
-    <col min="11522" max="11525" width="16.85546875" style="58" customWidth="1"/>
-    <col min="11526" max="11526" width="17.85546875" style="58" customWidth="1"/>
-    <col min="11527" max="11527" width="11.5703125" style="58" customWidth="1"/>
-    <col min="11528" max="11776" width="8.85546875" style="58"/>
-    <col min="11777" max="11777" width="21.85546875" style="58" customWidth="1"/>
-    <col min="11778" max="11781" width="16.85546875" style="58" customWidth="1"/>
-    <col min="11782" max="11782" width="17.85546875" style="58" customWidth="1"/>
-    <col min="11783" max="11783" width="11.5703125" style="58" customWidth="1"/>
-    <col min="11784" max="12032" width="8.85546875" style="58"/>
-    <col min="12033" max="12033" width="21.85546875" style="58" customWidth="1"/>
-    <col min="12034" max="12037" width="16.85546875" style="58" customWidth="1"/>
-    <col min="12038" max="12038" width="17.85546875" style="58" customWidth="1"/>
-    <col min="12039" max="12039" width="11.5703125" style="58" customWidth="1"/>
-    <col min="12040" max="12288" width="8.85546875" style="58"/>
-    <col min="12289" max="12289" width="21.85546875" style="58" customWidth="1"/>
-    <col min="12290" max="12293" width="16.85546875" style="58" customWidth="1"/>
-    <col min="12294" max="12294" width="17.85546875" style="58" customWidth="1"/>
-    <col min="12295" max="12295" width="11.5703125" style="58" customWidth="1"/>
-    <col min="12296" max="12544" width="8.85546875" style="58"/>
-    <col min="12545" max="12545" width="21.85546875" style="58" customWidth="1"/>
-    <col min="12546" max="12549" width="16.85546875" style="58" customWidth="1"/>
-    <col min="12550" max="12550" width="17.85546875" style="58" customWidth="1"/>
-    <col min="12551" max="12551" width="11.5703125" style="58" customWidth="1"/>
-    <col min="12552" max="12800" width="8.85546875" style="58"/>
-    <col min="12801" max="12801" width="21.85546875" style="58" customWidth="1"/>
-    <col min="12802" max="12805" width="16.85546875" style="58" customWidth="1"/>
-    <col min="12806" max="12806" width="17.85546875" style="58" customWidth="1"/>
-    <col min="12807" max="12807" width="11.5703125" style="58" customWidth="1"/>
-    <col min="12808" max="13056" width="8.85546875" style="58"/>
-    <col min="13057" max="13057" width="21.85546875" style="58" customWidth="1"/>
-    <col min="13058" max="13061" width="16.85546875" style="58" customWidth="1"/>
-    <col min="13062" max="13062" width="17.85546875" style="58" customWidth="1"/>
-    <col min="13063" max="13063" width="11.5703125" style="58" customWidth="1"/>
-    <col min="13064" max="13312" width="8.85546875" style="58"/>
-    <col min="13313" max="13313" width="21.85546875" style="58" customWidth="1"/>
-    <col min="13314" max="13317" width="16.85546875" style="58" customWidth="1"/>
-    <col min="13318" max="13318" width="17.85546875" style="58" customWidth="1"/>
-    <col min="13319" max="13319" width="11.5703125" style="58" customWidth="1"/>
-    <col min="13320" max="13568" width="8.85546875" style="58"/>
-    <col min="13569" max="13569" width="21.85546875" style="58" customWidth="1"/>
-    <col min="13570" max="13573" width="16.85546875" style="58" customWidth="1"/>
-    <col min="13574" max="13574" width="17.85546875" style="58" customWidth="1"/>
-    <col min="13575" max="13575" width="11.5703125" style="58" customWidth="1"/>
-    <col min="13576" max="13824" width="8.85546875" style="58"/>
-    <col min="13825" max="13825" width="21.85546875" style="58" customWidth="1"/>
-    <col min="13826" max="13829" width="16.85546875" style="58" customWidth="1"/>
-    <col min="13830" max="13830" width="17.85546875" style="58" customWidth="1"/>
-    <col min="13831" max="13831" width="11.5703125" style="58" customWidth="1"/>
-    <col min="13832" max="14080" width="8.85546875" style="58"/>
-    <col min="14081" max="14081" width="21.85546875" style="58" customWidth="1"/>
-    <col min="14082" max="14085" width="16.85546875" style="58" customWidth="1"/>
-    <col min="14086" max="14086" width="17.85546875" style="58" customWidth="1"/>
-    <col min="14087" max="14087" width="11.5703125" style="58" customWidth="1"/>
-    <col min="14088" max="14336" width="8.85546875" style="58"/>
-    <col min="14337" max="14337" width="21.85546875" style="58" customWidth="1"/>
-    <col min="14338" max="14341" width="16.85546875" style="58" customWidth="1"/>
-    <col min="14342" max="14342" width="17.85546875" style="58" customWidth="1"/>
-    <col min="14343" max="14343" width="11.5703125" style="58" customWidth="1"/>
-    <col min="14344" max="14592" width="8.85546875" style="58"/>
-    <col min="14593" max="14593" width="21.85546875" style="58" customWidth="1"/>
-    <col min="14594" max="14597" width="16.85546875" style="58" customWidth="1"/>
-    <col min="14598" max="14598" width="17.85546875" style="58" customWidth="1"/>
-    <col min="14599" max="14599" width="11.5703125" style="58" customWidth="1"/>
-    <col min="14600" max="14848" width="8.85546875" style="58"/>
-    <col min="14849" max="14849" width="21.85546875" style="58" customWidth="1"/>
-    <col min="14850" max="14853" width="16.85546875" style="58" customWidth="1"/>
-    <col min="14854" max="14854" width="17.85546875" style="58" customWidth="1"/>
-    <col min="14855" max="14855" width="11.5703125" style="58" customWidth="1"/>
-    <col min="14856" max="15104" width="8.85546875" style="58"/>
-    <col min="15105" max="15105" width="21.85546875" style="58" customWidth="1"/>
-    <col min="15106" max="15109" width="16.85546875" style="58" customWidth="1"/>
-    <col min="15110" max="15110" width="17.85546875" style="58" customWidth="1"/>
-    <col min="15111" max="15111" width="11.5703125" style="58" customWidth="1"/>
-    <col min="15112" max="15360" width="8.85546875" style="58"/>
-    <col min="15361" max="15361" width="21.85546875" style="58" customWidth="1"/>
-    <col min="15362" max="15365" width="16.85546875" style="58" customWidth="1"/>
-    <col min="15366" max="15366" width="17.85546875" style="58" customWidth="1"/>
-    <col min="15367" max="15367" width="11.5703125" style="58" customWidth="1"/>
-    <col min="15368" max="15616" width="8.85546875" style="58"/>
-    <col min="15617" max="15617" width="21.85546875" style="58" customWidth="1"/>
-    <col min="15618" max="15621" width="16.85546875" style="58" customWidth="1"/>
-    <col min="15622" max="15622" width="17.85546875" style="58" customWidth="1"/>
-    <col min="15623" max="15623" width="11.5703125" style="58" customWidth="1"/>
-    <col min="15624" max="15872" width="8.85546875" style="58"/>
-    <col min="15873" max="15873" width="21.85546875" style="58" customWidth="1"/>
-    <col min="15874" max="15877" width="16.85546875" style="58" customWidth="1"/>
-    <col min="15878" max="15878" width="17.85546875" style="58" customWidth="1"/>
-    <col min="15879" max="15879" width="11.5703125" style="58" customWidth="1"/>
-    <col min="15880" max="16128" width="8.85546875" style="58"/>
-    <col min="16129" max="16129" width="21.85546875" style="58" customWidth="1"/>
-    <col min="16130" max="16133" width="16.85546875" style="58" customWidth="1"/>
-    <col min="16134" max="16134" width="17.85546875" style="58" customWidth="1"/>
-    <col min="16135" max="16135" width="11.5703125" style="58" customWidth="1"/>
-    <col min="16136" max="16384" width="8.85546875" style="58"/>
+    <col min="1" max="1" width="21.875" style="58" customWidth="1"/>
+    <col min="2" max="5" width="16.875" style="58" customWidth="1"/>
+    <col min="6" max="6" width="17.875" style="58" customWidth="1"/>
+    <col min="7" max="7" width="11.5625" style="58" customWidth="1"/>
+    <col min="8" max="256" width="8.875" style="58"/>
+    <col min="257" max="257" width="21.875" style="58" customWidth="1"/>
+    <col min="258" max="261" width="16.875" style="58" customWidth="1"/>
+    <col min="262" max="262" width="17.875" style="58" customWidth="1"/>
+    <col min="263" max="263" width="11.5625" style="58" customWidth="1"/>
+    <col min="264" max="512" width="8.875" style="58"/>
+    <col min="513" max="513" width="21.875" style="58" customWidth="1"/>
+    <col min="514" max="517" width="16.875" style="58" customWidth="1"/>
+    <col min="518" max="518" width="17.875" style="58" customWidth="1"/>
+    <col min="519" max="519" width="11.5625" style="58" customWidth="1"/>
+    <col min="520" max="768" width="8.875" style="58"/>
+    <col min="769" max="769" width="21.875" style="58" customWidth="1"/>
+    <col min="770" max="773" width="16.875" style="58" customWidth="1"/>
+    <col min="774" max="774" width="17.875" style="58" customWidth="1"/>
+    <col min="775" max="775" width="11.5625" style="58" customWidth="1"/>
+    <col min="776" max="1024" width="8.875" style="58"/>
+    <col min="1025" max="1025" width="21.875" style="58" customWidth="1"/>
+    <col min="1026" max="1029" width="16.875" style="58" customWidth="1"/>
+    <col min="1030" max="1030" width="17.875" style="58" customWidth="1"/>
+    <col min="1031" max="1031" width="11.5625" style="58" customWidth="1"/>
+    <col min="1032" max="1280" width="8.875" style="58"/>
+    <col min="1281" max="1281" width="21.875" style="58" customWidth="1"/>
+    <col min="1282" max="1285" width="16.875" style="58" customWidth="1"/>
+    <col min="1286" max="1286" width="17.875" style="58" customWidth="1"/>
+    <col min="1287" max="1287" width="11.5625" style="58" customWidth="1"/>
+    <col min="1288" max="1536" width="8.875" style="58"/>
+    <col min="1537" max="1537" width="21.875" style="58" customWidth="1"/>
+    <col min="1538" max="1541" width="16.875" style="58" customWidth="1"/>
+    <col min="1542" max="1542" width="17.875" style="58" customWidth="1"/>
+    <col min="1543" max="1543" width="11.5625" style="58" customWidth="1"/>
+    <col min="1544" max="1792" width="8.875" style="58"/>
+    <col min="1793" max="1793" width="21.875" style="58" customWidth="1"/>
+    <col min="1794" max="1797" width="16.875" style="58" customWidth="1"/>
+    <col min="1798" max="1798" width="17.875" style="58" customWidth="1"/>
+    <col min="1799" max="1799" width="11.5625" style="58" customWidth="1"/>
+    <col min="1800" max="2048" width="8.875" style="58"/>
+    <col min="2049" max="2049" width="21.875" style="58" customWidth="1"/>
+    <col min="2050" max="2053" width="16.875" style="58" customWidth="1"/>
+    <col min="2054" max="2054" width="17.875" style="58" customWidth="1"/>
+    <col min="2055" max="2055" width="11.5625" style="58" customWidth="1"/>
+    <col min="2056" max="2304" width="8.875" style="58"/>
+    <col min="2305" max="2305" width="21.875" style="58" customWidth="1"/>
+    <col min="2306" max="2309" width="16.875" style="58" customWidth="1"/>
+    <col min="2310" max="2310" width="17.875" style="58" customWidth="1"/>
+    <col min="2311" max="2311" width="11.5625" style="58" customWidth="1"/>
+    <col min="2312" max="2560" width="8.875" style="58"/>
+    <col min="2561" max="2561" width="21.875" style="58" customWidth="1"/>
+    <col min="2562" max="2565" width="16.875" style="58" customWidth="1"/>
+    <col min="2566" max="2566" width="17.875" style="58" customWidth="1"/>
+    <col min="2567" max="2567" width="11.5625" style="58" customWidth="1"/>
+    <col min="2568" max="2816" width="8.875" style="58"/>
+    <col min="2817" max="2817" width="21.875" style="58" customWidth="1"/>
+    <col min="2818" max="2821" width="16.875" style="58" customWidth="1"/>
+    <col min="2822" max="2822" width="17.875" style="58" customWidth="1"/>
+    <col min="2823" max="2823" width="11.5625" style="58" customWidth="1"/>
+    <col min="2824" max="3072" width="8.875" style="58"/>
+    <col min="3073" max="3073" width="21.875" style="58" customWidth="1"/>
+    <col min="3074" max="3077" width="16.875" style="58" customWidth="1"/>
+    <col min="3078" max="3078" width="17.875" style="58" customWidth="1"/>
+    <col min="3079" max="3079" width="11.5625" style="58" customWidth="1"/>
+    <col min="3080" max="3328" width="8.875" style="58"/>
+    <col min="3329" max="3329" width="21.875" style="58" customWidth="1"/>
+    <col min="3330" max="3333" width="16.875" style="58" customWidth="1"/>
+    <col min="3334" max="3334" width="17.875" style="58" customWidth="1"/>
+    <col min="3335" max="3335" width="11.5625" style="58" customWidth="1"/>
+    <col min="3336" max="3584" width="8.875" style="58"/>
+    <col min="3585" max="3585" width="21.875" style="58" customWidth="1"/>
+    <col min="3586" max="3589" width="16.875" style="58" customWidth="1"/>
+    <col min="3590" max="3590" width="17.875" style="58" customWidth="1"/>
+    <col min="3591" max="3591" width="11.5625" style="58" customWidth="1"/>
+    <col min="3592" max="3840" width="8.875" style="58"/>
+    <col min="3841" max="3841" width="21.875" style="58" customWidth="1"/>
+    <col min="3842" max="3845" width="16.875" style="58" customWidth="1"/>
+    <col min="3846" max="3846" width="17.875" style="58" customWidth="1"/>
+    <col min="3847" max="3847" width="11.5625" style="58" customWidth="1"/>
+    <col min="3848" max="4096" width="8.875" style="58"/>
+    <col min="4097" max="4097" width="21.875" style="58" customWidth="1"/>
+    <col min="4098" max="4101" width="16.875" style="58" customWidth="1"/>
+    <col min="4102" max="4102" width="17.875" style="58" customWidth="1"/>
+    <col min="4103" max="4103" width="11.5625" style="58" customWidth="1"/>
+    <col min="4104" max="4352" width="8.875" style="58"/>
+    <col min="4353" max="4353" width="21.875" style="58" customWidth="1"/>
+    <col min="4354" max="4357" width="16.875" style="58" customWidth="1"/>
+    <col min="4358" max="4358" width="17.875" style="58" customWidth="1"/>
+    <col min="4359" max="4359" width="11.5625" style="58" customWidth="1"/>
+    <col min="4360" max="4608" width="8.875" style="58"/>
+    <col min="4609" max="4609" width="21.875" style="58" customWidth="1"/>
+    <col min="4610" max="4613" width="16.875" style="58" customWidth="1"/>
+    <col min="4614" max="4614" width="17.875" style="58" customWidth="1"/>
+    <col min="4615" max="4615" width="11.5625" style="58" customWidth="1"/>
+    <col min="4616" max="4864" width="8.875" style="58"/>
+    <col min="4865" max="4865" width="21.875" style="58" customWidth="1"/>
+    <col min="4866" max="4869" width="16.875" style="58" customWidth="1"/>
+    <col min="4870" max="4870" width="17.875" style="58" customWidth="1"/>
+    <col min="4871" max="4871" width="11.5625" style="58" customWidth="1"/>
+    <col min="4872" max="5120" width="8.875" style="58"/>
+    <col min="5121" max="5121" width="21.875" style="58" customWidth="1"/>
+    <col min="5122" max="5125" width="16.875" style="58" customWidth="1"/>
+    <col min="5126" max="5126" width="17.875" style="58" customWidth="1"/>
+    <col min="5127" max="5127" width="11.5625" style="58" customWidth="1"/>
+    <col min="5128" max="5376" width="8.875" style="58"/>
+    <col min="5377" max="5377" width="21.875" style="58" customWidth="1"/>
+    <col min="5378" max="5381" width="16.875" style="58" customWidth="1"/>
+    <col min="5382" max="5382" width="17.875" style="58" customWidth="1"/>
+    <col min="5383" max="5383" width="11.5625" style="58" customWidth="1"/>
+    <col min="5384" max="5632" width="8.875" style="58"/>
+    <col min="5633" max="5633" width="21.875" style="58" customWidth="1"/>
+    <col min="5634" max="5637" width="16.875" style="58" customWidth="1"/>
+    <col min="5638" max="5638" width="17.875" style="58" customWidth="1"/>
+    <col min="5639" max="5639" width="11.5625" style="58" customWidth="1"/>
+    <col min="5640" max="5888" width="8.875" style="58"/>
+    <col min="5889" max="5889" width="21.875" style="58" customWidth="1"/>
+    <col min="5890" max="5893" width="16.875" style="58" customWidth="1"/>
+    <col min="5894" max="5894" width="17.875" style="58" customWidth="1"/>
+    <col min="5895" max="5895" width="11.5625" style="58" customWidth="1"/>
+    <col min="5896" max="6144" width="8.875" style="58"/>
+    <col min="6145" max="6145" width="21.875" style="58" customWidth="1"/>
+    <col min="6146" max="6149" width="16.875" style="58" customWidth="1"/>
+    <col min="6150" max="6150" width="17.875" style="58" customWidth="1"/>
+    <col min="6151" max="6151" width="11.5625" style="58" customWidth="1"/>
+    <col min="6152" max="6400" width="8.875" style="58"/>
+    <col min="6401" max="6401" width="21.875" style="58" customWidth="1"/>
+    <col min="6402" max="6405" width="16.875" style="58" customWidth="1"/>
+    <col min="6406" max="6406" width="17.875" style="58" customWidth="1"/>
+    <col min="6407" max="6407" width="11.5625" style="58" customWidth="1"/>
+    <col min="6408" max="6656" width="8.875" style="58"/>
+    <col min="6657" max="6657" width="21.875" style="58" customWidth="1"/>
+    <col min="6658" max="6661" width="16.875" style="58" customWidth="1"/>
+    <col min="6662" max="6662" width="17.875" style="58" customWidth="1"/>
+    <col min="6663" max="6663" width="11.5625" style="58" customWidth="1"/>
+    <col min="6664" max="6912" width="8.875" style="58"/>
+    <col min="6913" max="6913" width="21.875" style="58" customWidth="1"/>
+    <col min="6914" max="6917" width="16.875" style="58" customWidth="1"/>
+    <col min="6918" max="6918" width="17.875" style="58" customWidth="1"/>
+    <col min="6919" max="6919" width="11.5625" style="58" customWidth="1"/>
+    <col min="6920" max="7168" width="8.875" style="58"/>
+    <col min="7169" max="7169" width="21.875" style="58" customWidth="1"/>
+    <col min="7170" max="7173" width="16.875" style="58" customWidth="1"/>
+    <col min="7174" max="7174" width="17.875" style="58" customWidth="1"/>
+    <col min="7175" max="7175" width="11.5625" style="58" customWidth="1"/>
+    <col min="7176" max="7424" width="8.875" style="58"/>
+    <col min="7425" max="7425" width="21.875" style="58" customWidth="1"/>
+    <col min="7426" max="7429" width="16.875" style="58" customWidth="1"/>
+    <col min="7430" max="7430" width="17.875" style="58" customWidth="1"/>
+    <col min="7431" max="7431" width="11.5625" style="58" customWidth="1"/>
+    <col min="7432" max="7680" width="8.875" style="58"/>
+    <col min="7681" max="7681" width="21.875" style="58" customWidth="1"/>
+    <col min="7682" max="7685" width="16.875" style="58" customWidth="1"/>
+    <col min="7686" max="7686" width="17.875" style="58" customWidth="1"/>
+    <col min="7687" max="7687" width="11.5625" style="58" customWidth="1"/>
+    <col min="7688" max="7936" width="8.875" style="58"/>
+    <col min="7937" max="7937" width="21.875" style="58" customWidth="1"/>
+    <col min="7938" max="7941" width="16.875" style="58" customWidth="1"/>
+    <col min="7942" max="7942" width="17.875" style="58" customWidth="1"/>
+    <col min="7943" max="7943" width="11.5625" style="58" customWidth="1"/>
+    <col min="7944" max="8192" width="8.875" style="58"/>
+    <col min="8193" max="8193" width="21.875" style="58" customWidth="1"/>
+    <col min="8194" max="8197" width="16.875" style="58" customWidth="1"/>
+    <col min="8198" max="8198" width="17.875" style="58" customWidth="1"/>
+    <col min="8199" max="8199" width="11.5625" style="58" customWidth="1"/>
+    <col min="8200" max="8448" width="8.875" style="58"/>
+    <col min="8449" max="8449" width="21.875" style="58" customWidth="1"/>
+    <col min="8450" max="8453" width="16.875" style="58" customWidth="1"/>
+    <col min="8454" max="8454" width="17.875" style="58" customWidth="1"/>
+    <col min="8455" max="8455" width="11.5625" style="58" customWidth="1"/>
+    <col min="8456" max="8704" width="8.875" style="58"/>
+    <col min="8705" max="8705" width="21.875" style="58" customWidth="1"/>
+    <col min="8706" max="8709" width="16.875" style="58" customWidth="1"/>
+    <col min="8710" max="8710" width="17.875" style="58" customWidth="1"/>
+    <col min="8711" max="8711" width="11.5625" style="58" customWidth="1"/>
+    <col min="8712" max="8960" width="8.875" style="58"/>
+    <col min="8961" max="8961" width="21.875" style="58" customWidth="1"/>
+    <col min="8962" max="8965" width="16.875" style="58" customWidth="1"/>
+    <col min="8966" max="8966" width="17.875" style="58" customWidth="1"/>
+    <col min="8967" max="8967" width="11.5625" style="58" customWidth="1"/>
+    <col min="8968" max="9216" width="8.875" style="58"/>
+    <col min="9217" max="9217" width="21.875" style="58" customWidth="1"/>
+    <col min="9218" max="9221" width="16.875" style="58" customWidth="1"/>
+    <col min="9222" max="9222" width="17.875" style="58" customWidth="1"/>
+    <col min="9223" max="9223" width="11.5625" style="58" customWidth="1"/>
+    <col min="9224" max="9472" width="8.875" style="58"/>
+    <col min="9473" max="9473" width="21.875" style="58" customWidth="1"/>
+    <col min="9474" max="9477" width="16.875" style="58" customWidth="1"/>
+    <col min="9478" max="9478" width="17.875" style="58" customWidth="1"/>
+    <col min="9479" max="9479" width="11.5625" style="58" customWidth="1"/>
+    <col min="9480" max="9728" width="8.875" style="58"/>
+    <col min="9729" max="9729" width="21.875" style="58" customWidth="1"/>
+    <col min="9730" max="9733" width="16.875" style="58" customWidth="1"/>
+    <col min="9734" max="9734" width="17.875" style="58" customWidth="1"/>
+    <col min="9735" max="9735" width="11.5625" style="58" customWidth="1"/>
+    <col min="9736" max="9984" width="8.875" style="58"/>
+    <col min="9985" max="9985" width="21.875" style="58" customWidth="1"/>
+    <col min="9986" max="9989" width="16.875" style="58" customWidth="1"/>
+    <col min="9990" max="9990" width="17.875" style="58" customWidth="1"/>
+    <col min="9991" max="9991" width="11.5625" style="58" customWidth="1"/>
+    <col min="9992" max="10240" width="8.875" style="58"/>
+    <col min="10241" max="10241" width="21.875" style="58" customWidth="1"/>
+    <col min="10242" max="10245" width="16.875" style="58" customWidth="1"/>
+    <col min="10246" max="10246" width="17.875" style="58" customWidth="1"/>
+    <col min="10247" max="10247" width="11.5625" style="58" customWidth="1"/>
+    <col min="10248" max="10496" width="8.875" style="58"/>
+    <col min="10497" max="10497" width="21.875" style="58" customWidth="1"/>
+    <col min="10498" max="10501" width="16.875" style="58" customWidth="1"/>
+    <col min="10502" max="10502" width="17.875" style="58" customWidth="1"/>
+    <col min="10503" max="10503" width="11.5625" style="58" customWidth="1"/>
+    <col min="10504" max="10752" width="8.875" style="58"/>
+    <col min="10753" max="10753" width="21.875" style="58" customWidth="1"/>
+    <col min="10754" max="10757" width="16.875" style="58" customWidth="1"/>
+    <col min="10758" max="10758" width="17.875" style="58" customWidth="1"/>
+    <col min="10759" max="10759" width="11.5625" style="58" customWidth="1"/>
+    <col min="10760" max="11008" width="8.875" style="58"/>
+    <col min="11009" max="11009" width="21.875" style="58" customWidth="1"/>
+    <col min="11010" max="11013" width="16.875" style="58" customWidth="1"/>
+    <col min="11014" max="11014" width="17.875" style="58" customWidth="1"/>
+    <col min="11015" max="11015" width="11.5625" style="58" customWidth="1"/>
+    <col min="11016" max="11264" width="8.875" style="58"/>
+    <col min="11265" max="11265" width="21.875" style="58" customWidth="1"/>
+    <col min="11266" max="11269" width="16.875" style="58" customWidth="1"/>
+    <col min="11270" max="11270" width="17.875" style="58" customWidth="1"/>
+    <col min="11271" max="11271" width="11.5625" style="58" customWidth="1"/>
+    <col min="11272" max="11520" width="8.875" style="58"/>
+    <col min="11521" max="11521" width="21.875" style="58" customWidth="1"/>
+    <col min="11522" max="11525" width="16.875" style="58" customWidth="1"/>
+    <col min="11526" max="11526" width="17.875" style="58" customWidth="1"/>
+    <col min="11527" max="11527" width="11.5625" style="58" customWidth="1"/>
+    <col min="11528" max="11776" width="8.875" style="58"/>
+    <col min="11777" max="11777" width="21.875" style="58" customWidth="1"/>
+    <col min="11778" max="11781" width="16.875" style="58" customWidth="1"/>
+    <col min="11782" max="11782" width="17.875" style="58" customWidth="1"/>
+    <col min="11783" max="11783" width="11.5625" style="58" customWidth="1"/>
+    <col min="11784" max="12032" width="8.875" style="58"/>
+    <col min="12033" max="12033" width="21.875" style="58" customWidth="1"/>
+    <col min="12034" max="12037" width="16.875" style="58" customWidth="1"/>
+    <col min="12038" max="12038" width="17.875" style="58" customWidth="1"/>
+    <col min="12039" max="12039" width="11.5625" style="58" customWidth="1"/>
+    <col min="12040" max="12288" width="8.875" style="58"/>
+    <col min="12289" max="12289" width="21.875" style="58" customWidth="1"/>
+    <col min="12290" max="12293" width="16.875" style="58" customWidth="1"/>
+    <col min="12294" max="12294" width="17.875" style="58" customWidth="1"/>
+    <col min="12295" max="12295" width="11.5625" style="58" customWidth="1"/>
+    <col min="12296" max="12544" width="8.875" style="58"/>
+    <col min="12545" max="12545" width="21.875" style="58" customWidth="1"/>
+    <col min="12546" max="12549" width="16.875" style="58" customWidth="1"/>
+    <col min="12550" max="12550" width="17.875" style="58" customWidth="1"/>
+    <col min="12551" max="12551" width="11.5625" style="58" customWidth="1"/>
+    <col min="12552" max="12800" width="8.875" style="58"/>
+    <col min="12801" max="12801" width="21.875" style="58" customWidth="1"/>
+    <col min="12802" max="12805" width="16.875" style="58" customWidth="1"/>
+    <col min="12806" max="12806" width="17.875" style="58" customWidth="1"/>
+    <col min="12807" max="12807" width="11.5625" style="58" customWidth="1"/>
+    <col min="12808" max="13056" width="8.875" style="58"/>
+    <col min="13057" max="13057" width="21.875" style="58" customWidth="1"/>
+    <col min="13058" max="13061" width="16.875" style="58" customWidth="1"/>
+    <col min="13062" max="13062" width="17.875" style="58" customWidth="1"/>
+    <col min="13063" max="13063" width="11.5625" style="58" customWidth="1"/>
+    <col min="13064" max="13312" width="8.875" style="58"/>
+    <col min="13313" max="13313" width="21.875" style="58" customWidth="1"/>
+    <col min="13314" max="13317" width="16.875" style="58" customWidth="1"/>
+    <col min="13318" max="13318" width="17.875" style="58" customWidth="1"/>
+    <col min="13319" max="13319" width="11.5625" style="58" customWidth="1"/>
+    <col min="13320" max="13568" width="8.875" style="58"/>
+    <col min="13569" max="13569" width="21.875" style="58" customWidth="1"/>
+    <col min="13570" max="13573" width="16.875" style="58" customWidth="1"/>
+    <col min="13574" max="13574" width="17.875" style="58" customWidth="1"/>
+    <col min="13575" max="13575" width="11.5625" style="58" customWidth="1"/>
+    <col min="13576" max="13824" width="8.875" style="58"/>
+    <col min="13825" max="13825" width="21.875" style="58" customWidth="1"/>
+    <col min="13826" max="13829" width="16.875" style="58" customWidth="1"/>
+    <col min="13830" max="13830" width="17.875" style="58" customWidth="1"/>
+    <col min="13831" max="13831" width="11.5625" style="58" customWidth="1"/>
+    <col min="13832" max="14080" width="8.875" style="58"/>
+    <col min="14081" max="14081" width="21.875" style="58" customWidth="1"/>
+    <col min="14082" max="14085" width="16.875" style="58" customWidth="1"/>
+    <col min="14086" max="14086" width="17.875" style="58" customWidth="1"/>
+    <col min="14087" max="14087" width="11.5625" style="58" customWidth="1"/>
+    <col min="14088" max="14336" width="8.875" style="58"/>
+    <col min="14337" max="14337" width="21.875" style="58" customWidth="1"/>
+    <col min="14338" max="14341" width="16.875" style="58" customWidth="1"/>
+    <col min="14342" max="14342" width="17.875" style="58" customWidth="1"/>
+    <col min="14343" max="14343" width="11.5625" style="58" customWidth="1"/>
+    <col min="14344" max="14592" width="8.875" style="58"/>
+    <col min="14593" max="14593" width="21.875" style="58" customWidth="1"/>
+    <col min="14594" max="14597" width="16.875" style="58" customWidth="1"/>
+    <col min="14598" max="14598" width="17.875" style="58" customWidth="1"/>
+    <col min="14599" max="14599" width="11.5625" style="58" customWidth="1"/>
+    <col min="14600" max="14848" width="8.875" style="58"/>
+    <col min="14849" max="14849" width="21.875" style="58" customWidth="1"/>
+    <col min="14850" max="14853" width="16.875" style="58" customWidth="1"/>
+    <col min="14854" max="14854" width="17.875" style="58" customWidth="1"/>
+    <col min="14855" max="14855" width="11.5625" style="58" customWidth="1"/>
+    <col min="14856" max="15104" width="8.875" style="58"/>
+    <col min="15105" max="15105" width="21.875" style="58" customWidth="1"/>
+    <col min="15106" max="15109" width="16.875" style="58" customWidth="1"/>
+    <col min="15110" max="15110" width="17.875" style="58" customWidth="1"/>
+    <col min="15111" max="15111" width="11.5625" style="58" customWidth="1"/>
+    <col min="15112" max="15360" width="8.875" style="58"/>
+    <col min="15361" max="15361" width="21.875" style="58" customWidth="1"/>
+    <col min="15362" max="15365" width="16.875" style="58" customWidth="1"/>
+    <col min="15366" max="15366" width="17.875" style="58" customWidth="1"/>
+    <col min="15367" max="15367" width="11.5625" style="58" customWidth="1"/>
+    <col min="15368" max="15616" width="8.875" style="58"/>
+    <col min="15617" max="15617" width="21.875" style="58" customWidth="1"/>
+    <col min="15618" max="15621" width="16.875" style="58" customWidth="1"/>
+    <col min="15622" max="15622" width="17.875" style="58" customWidth="1"/>
+    <col min="15623" max="15623" width="11.5625" style="58" customWidth="1"/>
+    <col min="15624" max="15872" width="8.875" style="58"/>
+    <col min="15873" max="15873" width="21.875" style="58" customWidth="1"/>
+    <col min="15874" max="15877" width="16.875" style="58" customWidth="1"/>
+    <col min="15878" max="15878" width="17.875" style="58" customWidth="1"/>
+    <col min="15879" max="15879" width="11.5625" style="58" customWidth="1"/>
+    <col min="15880" max="16128" width="8.875" style="58"/>
+    <col min="16129" max="16129" width="21.875" style="58" customWidth="1"/>
+    <col min="16130" max="16133" width="16.875" style="58" customWidth="1"/>
+    <col min="16134" max="16134" width="17.875" style="58" customWidth="1"/>
+    <col min="16135" max="16135" width="11.5625" style="58" customWidth="1"/>
+    <col min="16136" max="16384" width="8.875" style="58"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="57" t="s">
         <v>157</v>
       </c>
       <c r="H1" s="59"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="H2" s="59"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="60" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B4" s="61" t="s">
         <v>159</v>
       </c>
@@ -5679,7 +5905,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="58" t="s">
         <v>162</v>
       </c>
@@ -5693,7 +5919,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="58" t="s">
         <v>163</v>
       </c>
@@ -5707,7 +5933,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="58" t="s">
         <v>164</v>
       </c>
@@ -5733,7 +5959,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="58" t="s">
         <v>159</v>
       </c>
@@ -5753,7 +5979,7 @@
       <c r="H9" s="64"/>
       <c r="I9" s="65"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="58" t="s">
         <v>160</v>
       </c>
@@ -5772,7 +5998,7 @@
       <c r="G10" s="66"/>
       <c r="I10" s="67"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="58" t="s">
         <v>161</v>
       </c>
@@ -5792,12 +6018,12 @@
       <c r="H11" s="69"/>
       <c r="I11" s="70"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="71" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" s="61" t="s">
         <v>159</v>
       </c>
@@ -5811,7 +6037,7 @@
       <c r="F14" s="57"/>
       <c r="G14" s="72"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="73" t="s">
         <v>167</v>
       </c>
@@ -5820,16 +6046,16 @@
       <c r="D15" s="74"/>
       <c r="F15" s="73"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="F16" s="75"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="71" t="s">
         <v>168</v>
       </c>
       <c r="F17" s="75"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="72" t="s">
         <v>169</v>
       </c>
@@ -5839,21 +6065,21 @@
       </c>
       <c r="F18" s="75"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="76"/>
       <c r="C19" s="77"/>
       <c r="D19" s="78"/>
       <c r="F19" s="75"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="F20" s="75"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="57" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B22" s="72" t="s">
         <v>172</v>
       </c>
@@ -5862,26 +6088,26 @@
         <v>173</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B23" s="76"/>
       <c r="C23" s="79"/>
       <c r="D23" s="80">
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="71" t="s">
         <v>174</v>
       </c>
       <c r="B25" s="81"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="58" t="s">
         <v>175</v>
       </c>
       <c r="B26" s="81"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="71"/>
     </row>
   </sheetData>
@@ -5891,15 +6117,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBB85EF8-765A-4E8F-8890-3D210C509914}">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.4375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>52</v>
       </c>
@@ -5907,18 +6133,22 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>196</v>
       </c>
       <c r="B2" s="41">
-        <v>330.58427824258496</v>
+        <v>330.32553318164355</v>
       </c>
       <c r="C2" s="41">
-        <v>923.59909391470558</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>923.75928147692673</v>
+      </c>
+      <c r="K2">
+        <f>_xlfn.NORM.INV(0.05, 10000, 1100)</f>
+        <v>8190.6610103533803</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>197</v>
       </c>
@@ -5928,12 +6158,16 @@
       <c r="C3" s="83">
         <v>129</v>
       </c>
-      <c r="D3" s="84">
+      <c r="D3" s="96">
         <f>SUMPRODUCT($B$2:$C$2,B3:C3)</f>
-        <v>145591.02537440381</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>145590.98996505502</v>
+      </c>
+      <c r="K3">
+        <f>_xlfn.NORM.INV(0.01, 3000, 270)</f>
+        <v>2371.8860740089731</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>198</v>
       </c>
@@ -5945,24 +6179,24 @@
       </c>
       <c r="D4">
         <f t="shared" ref="D4:D5" si="0">SUMPRODUCT($B$2:$C$2,B4:C4)</f>
-        <v>7194.515954701159</v>
+        <v>7194.1833547697779</v>
       </c>
       <c r="E4">
         <f>_xlfn.NORM.S.INV(0.9)*SQRT(SUMPRODUCT(B10:C10,B11:C11))</f>
-        <v>2805.4942707386172</v>
-      </c>
-      <c r="F4">
+        <v>2805.8243247005807</v>
+      </c>
+      <c r="F4" s="95">
         <f>D4+E4</f>
-        <v>10000.010225439775</v>
+        <v>10000.007679470358</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="86">
         <v>10000</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>199</v>
       </c>
@@ -5974,20 +6208,20 @@
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>2177.7824660719962</v>
-      </c>
-      <c r="F5">
+        <v>2177.8440961354972</v>
+      </c>
+      <c r="F5" s="95">
         <f>D5+E5</f>
-        <v>2177.7824660719962</v>
+        <v>2177.8440961354972</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="86">
         <v>3000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>200</v>
       </c>
@@ -5998,7 +6232,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>145</v>
       </c>
@@ -6009,7 +6243,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>196</v>
       </c>
@@ -6022,17 +6256,17 @@
         <v>5.2899999999999991</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>201</v>
       </c>
       <c r="B11">
         <f>B2^2</f>
-        <v>109285.96502117084</v>
+        <v>109114.95787173709</v>
       </c>
       <c r="C11">
         <f>C2^2</f>
-        <v>853035.28628006508</v>
+        <v>853331.21011476789</v>
       </c>
     </row>
   </sheetData>
@@ -6043,17 +6277,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDFD6E9F-BD43-4942-8E37-229285165C89}">
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -6067,24 +6301,24 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="8"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>32</v>
       </c>
       <c r="B6" s="9"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -6093,7 +6327,7 @@
         <v>Sell</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f>B8</f>
         <v>Sell</v>
@@ -6138,97 +6372,97 @@
         <v>160</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>0.15000000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>0.2</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>0.25</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>0.3</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <v>0.35000000000000003</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>0.45</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>0.5</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>0.60000000000000009</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>0.65000000000000013</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>0.70000000000000007</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>0.75000000000000011</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>0.8</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>0.85000000000000009</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>0.90000000000000013</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>0.95000000000000007</v>
       </c>
@@ -6280,13 +6514,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D02281E-1859-4FDF-B839-FBB178FB7475}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.4375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1" s="87" t="s">
         <v>89</v>
       </c>
@@ -6294,7 +6528,7 @@
       <c r="E1" s="87"/>
       <c r="F1" s="87"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C2" s="87" t="s">
         <v>90</v>
       </c>
@@ -6302,7 +6536,7 @@
       <c r="E2" s="87"/>
       <c r="F2" s="87"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
         <v>91</v>
       </c>
@@ -6316,7 +6550,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
         <v>92</v>
       </c>
@@ -6328,7 +6562,7 @@
       </c>
       <c r="F4" s="87"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="87"/>
       <c r="B5" t="s">
         <v>97</v>
@@ -6344,7 +6578,7 @@
       </c>
       <c r="F5" s="13"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="87"/>
       <c r="B6" t="s">
         <v>98</v>
@@ -6360,7 +6594,7 @@
       </c>
       <c r="F6" s="13"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="87"/>
       <c r="B7" t="s">
         <v>99</v>
@@ -6376,13 +6610,13 @@
       </c>
       <c r="F7" s="13"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="87" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="87"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>98</v>
       </c>
@@ -6396,7 +6630,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>99</v>
       </c>
@@ -6426,15 +6660,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34FD0729-EC8E-4CFF-8049-7EF09D1893D6}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.4375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>192</v>
       </c>
@@ -6448,7 +6682,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>183</v>
       </c>
@@ -6462,7 +6696,7 @@
         <v>6000000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>184</v>
       </c>
@@ -6476,7 +6710,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>185</v>
       </c>
@@ -6490,7 +6724,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>186</v>
       </c>
@@ -6504,7 +6738,7 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>187</v>
       </c>
@@ -6518,7 +6752,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>188</v>
       </c>
@@ -6532,7 +6766,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>189</v>
       </c>
@@ -6546,7 +6780,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>190</v>
       </c>
@@ -6560,7 +6794,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>191</v>
       </c>
@@ -6582,17 +6816,17 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.4375" customWidth="1"/>
+    <col min="4" max="4" width="11.5625" customWidth="1"/>
+    <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>19</v>
       </c>
@@ -6600,7 +6834,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6617,7 +6851,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -6632,7 +6866,7 @@
       <c r="I3" s="36"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -6643,12 +6877,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -6659,7 +6893,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -6673,7 +6907,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6687,7 +6921,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -6701,26 +6935,26 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" s="2"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -6728,7 +6962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="1"/>
     </row>
   </sheetData>
@@ -6737,6 +6971,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005D21A9346877C94FBE0D2EF98A54C8DF" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b9d30dfdbb3c728c42ac273b0b267a13">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0f411969-aaa6-47b2-a14e-e9510c0df77f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ca649492ee4635bde6ac1a281be3e98b" ns2:_="">
     <xsd:import namespace="0f411969-aaa6-47b2-a14e-e9510c0df77f"/>
@@ -6874,22 +7123,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{045A6F27-BBFE-48F3-BE55-9FF8155F59CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4499BA0A-D035-4121-AEC6-666388DF038D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7471329D-8B35-4081-B86A-5ED8B1A94B51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6905,21 +7156,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4499BA0A-D035-4121-AEC6-666388DF038D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{045A6F27-BBFE-48F3-BE55-9FF8155F59CF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/class_excel/decision-making-under-uncertainty.xlsx
+++ b/class_excel/decision-making-under-uncertainty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E302939E-6BAB-4A63-A50A-343490242E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7295D138-A250-4C08-8878-2CB574E241B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="805" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="805" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Variability" sheetId="14" r:id="rId1"/>
@@ -1121,7 +1121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1148,17 +1148,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -1328,13 +1317,13 @@
     <xf numFmtId="187" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1355,7 +1344,8 @@
     <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1366,25 +1356,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="190" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1407,7 +1394,7 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="192" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1420,6 +1407,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1"/>
@@ -1427,7 +1415,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1451,27 +1438,25 @@
     <xf numFmtId="191" fontId="8" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - Accent1" xfId="2" builtinId="30"/>
@@ -1883,21 +1868,21 @@
       <c r="B4">
         <v>100</v>
       </c>
-      <c r="C4" s="54">
+      <c r="C4" s="52">
         <f>(B4-$B$16)^2</f>
         <v>0</v>
       </c>
       <c r="E4">
         <v>102.61</v>
       </c>
-      <c r="F4" s="55">
+      <c r="F4" s="53">
         <f t="shared" ref="F4:F13" si="0">(E4-$E$16)^2</f>
         <v>6.3857290000000049</v>
       </c>
       <c r="H4">
         <v>103.21</v>
       </c>
-      <c r="I4" s="55">
+      <c r="I4" s="53">
         <f t="shared" ref="I4:I13" si="1">(H4-$H$16)^2</f>
         <v>9.8344960000000619</v>
       </c>
@@ -1909,21 +1894,21 @@
       <c r="B5">
         <v>100</v>
       </c>
-      <c r="C5" s="54">
+      <c r="C5" s="52">
         <f t="shared" ref="C5:C13" si="2">(B5-$B$16)^2</f>
         <v>0</v>
       </c>
       <c r="E5">
         <v>103.25</v>
       </c>
-      <c r="F5" s="55">
+      <c r="F5" s="53">
         <f t="shared" si="0"/>
         <v>10.02988900000001</v>
       </c>
       <c r="H5">
         <v>93.66</v>
       </c>
-      <c r="I5" s="55">
+      <c r="I5" s="53">
         <f t="shared" si="1"/>
         <v>41.139395999999834</v>
       </c>
@@ -1935,21 +1920,21 @@
       <c r="B6">
         <v>100</v>
       </c>
-      <c r="C6" s="54">
+      <c r="C6" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E6">
         <v>96.34</v>
       </c>
-      <c r="F6" s="55">
+      <c r="F6" s="53">
         <f t="shared" si="0"/>
         <v>14.010048999999963</v>
       </c>
       <c r="H6">
         <v>120.87</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="53">
         <f t="shared" si="1"/>
         <v>432.47361600000085</v>
       </c>
@@ -1961,21 +1946,21 @@
       <c r="B7">
         <v>100</v>
       </c>
-      <c r="C7" s="54">
+      <c r="C7" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E7">
         <v>96.27</v>
       </c>
-      <c r="F7" s="55">
+      <c r="F7" s="53">
         <f t="shared" si="0"/>
         <v>14.538969000000018</v>
       </c>
       <c r="H7">
         <v>110.26</v>
       </c>
-      <c r="I7" s="55">
+      <c r="I7" s="53">
         <f t="shared" si="1"/>
         <v>103.75459600000043</v>
       </c>
@@ -1987,21 +1972,21 @@
       <c r="B8">
         <v>100</v>
       </c>
-      <c r="C8" s="54">
+      <c r="C8" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E8">
         <v>103.77</v>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="53">
         <f t="shared" si="0"/>
         <v>13.593968999999982</v>
       </c>
       <c r="H8">
         <v>117.31</v>
       </c>
-      <c r="I8" s="55">
+      <c r="I8" s="53">
         <f t="shared" si="1"/>
         <v>297.07969600000064</v>
       </c>
@@ -2013,21 +1998,21 @@
       <c r="B9">
         <v>100</v>
       </c>
-      <c r="C9" s="54">
+      <c r="C9" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E9">
         <v>97.45</v>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="53">
         <f t="shared" si="0"/>
         <v>6.9326889999999768</v>
       </c>
       <c r="H9">
         <v>110.23</v>
       </c>
-      <c r="I9" s="55">
+      <c r="I9" s="53">
         <f t="shared" si="1"/>
         <v>103.14433600000041</v>
       </c>
@@ -2039,21 +2024,21 @@
       <c r="B10">
         <v>100</v>
       </c>
-      <c r="C10" s="54">
+      <c r="C10" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E10">
         <v>98.22</v>
       </c>
-      <c r="F10" s="55">
+      <c r="F10" s="53">
         <f t="shared" si="0"/>
         <v>3.4707689999999984</v>
       </c>
       <c r="H10">
         <v>70.540000000000006</v>
       </c>
-      <c r="I10" s="55">
+      <c r="I10" s="53">
         <f t="shared" si="1"/>
         <v>872.25715599999864</v>
       </c>
@@ -2065,21 +2050,21 @@
       <c r="B11">
         <v>100</v>
       </c>
-      <c r="C11" s="54">
+      <c r="C11" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E11">
         <v>102.76</v>
       </c>
-      <c r="F11" s="55">
+      <c r="F11" s="53">
         <f t="shared" si="0"/>
         <v>7.1663290000000357</v>
       </c>
       <c r="H11">
         <v>39.53</v>
       </c>
-      <c r="I11" s="55">
+      <c r="I11" s="53">
         <f t="shared" si="1"/>
         <v>3665.5759359999979</v>
       </c>
@@ -2091,21 +2076,21 @@
       <c r="B12">
         <v>100</v>
       </c>
-      <c r="C12" s="54">
+      <c r="C12" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E12">
         <v>101.56</v>
       </c>
-      <c r="F12" s="55">
+      <c r="F12" s="53">
         <f t="shared" si="0"/>
         <v>2.1815290000000114</v>
       </c>
       <c r="H12">
         <v>133.22</v>
       </c>
-      <c r="I12" s="55">
+      <c r="I12" s="53">
         <f t="shared" si="1"/>
         <v>1098.6573160000009</v>
       </c>
@@ -2117,21 +2102,21 @@
       <c r="B13">
         <v>100</v>
       </c>
-      <c r="C13" s="54">
+      <c r="C13" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E13">
         <v>98.6</v>
       </c>
-      <c r="F13" s="55">
+      <c r="F13" s="53">
         <f t="shared" si="0"/>
         <v>2.1992890000000123</v>
       </c>
       <c r="H13">
         <v>101.91</v>
       </c>
-      <c r="I13" s="55">
+      <c r="I13" s="53">
         <f t="shared" si="1"/>
         <v>3.3708960000000467</v>
       </c>
@@ -2173,28 +2158,28 @@
       </c>
     </row>
     <row r="19" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="48">
+      <c r="B19" s="46">
         <f>SUM(C4:C13)/9</f>
         <v>0</v>
       </c>
-      <c r="C19" s="48">
+      <c r="C19" s="46">
         <f>_xlfn.VAR.S(B4:B13)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48">
+      <c r="D19" s="46"/>
+      <c r="E19" s="46">
         <f>SUM(F4:F13)/9</f>
         <v>8.9454677777777789</v>
       </c>
-      <c r="F19" s="48">
+      <c r="F19" s="46">
         <f>_xlfn.VAR.S(E4:E13)</f>
         <v>8.9454677777777789</v>
       </c>
-      <c r="H19" s="48">
+      <c r="H19" s="46">
         <f>SUM(I4:I13)/9</f>
         <v>736.36527111111116</v>
       </c>
-      <c r="I19" s="48">
+      <c r="I19" s="46">
         <f>_xlfn.VAR.S(H4:H13)</f>
         <v>736.36527111111434</v>
       </c>
@@ -2211,28 +2196,28 @@
       </c>
     </row>
     <row r="22" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="48">
+      <c r="B22" s="46">
         <f>SUM(C4:C13)/10</f>
         <v>0</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="46">
         <f>_xlfn.VAR.P(B4:B13)</f>
         <v>0</v>
       </c>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48">
+      <c r="D22" s="46"/>
+      <c r="E22" s="46">
         <f>SUM(F4:F13)/10</f>
         <v>8.0509210000000007</v>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="46">
         <f>_xlfn.VAR.P(E4:E13)</f>
         <v>8.0509210000000007</v>
       </c>
-      <c r="H22" s="48">
+      <c r="H22" s="46">
         <f>SUM(I4:I13)/10</f>
         <v>662.72874400000001</v>
       </c>
-      <c r="I22" s="48">
+      <c r="I22" s="46">
         <f>_xlfn.VAR.P(H4:H13)</f>
         <v>662.72874400000433</v>
       </c>
@@ -2249,28 +2234,28 @@
       </c>
     </row>
     <row r="25" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="48">
+      <c r="B25" s="46">
         <f>SQRT(B19)</f>
         <v>0</v>
       </c>
-      <c r="C25" s="48">
+      <c r="C25" s="46">
         <f>_xlfn.STDEV.S(B4:B13)</f>
         <v>0</v>
       </c>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48">
+      <c r="D25" s="46"/>
+      <c r="E25" s="46">
         <f>SQRT(E19)</f>
         <v>2.9908974870058285</v>
       </c>
-      <c r="F25" s="48">
+      <c r="F25" s="46">
         <f>_xlfn.STDEV.S(E4:E13)</f>
         <v>2.9908974870058285</v>
       </c>
-      <c r="H25" s="48">
+      <c r="H25" s="46">
         <f>SQRT(H19)</f>
         <v>27.13605113333757</v>
       </c>
-      <c r="I25" s="48">
+      <c r="I25" s="46">
         <f>_xlfn.STDEV.S(H4:H13)</f>
         <v>27.136051133337627</v>
       </c>
@@ -2287,28 +2272,28 @@
       </c>
     </row>
     <row r="28" spans="2:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="48">
+      <c r="B28" s="46">
         <f>SQRT(B22)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="48">
+      <c r="C28" s="46">
         <f>_xlfn.STDEV.P(B4:B13)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48">
+      <c r="D28" s="46"/>
+      <c r="E28" s="46">
         <f>SQRT(E22)</f>
         <v>2.837414492103683</v>
       </c>
-      <c r="F28" s="48">
+      <c r="F28" s="46">
         <f>_xlfn.STDEV.P(E4:E13)</f>
         <v>2.837414492103683</v>
       </c>
-      <c r="H28" s="48">
+      <c r="H28" s="46">
         <f>SQRT(H22)</f>
         <v>25.743518485242067</v>
       </c>
-      <c r="I28" s="48">
+      <c r="I28" s="46">
         <f>_xlfn.STDEV.P(H4:H13)</f>
         <v>25.743518485242152</v>
       </c>
@@ -2404,7 +2389,7 @@
         <f>D6-$B$2</f>
         <v>4800000</v>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="46">
         <f>1-EXP(-(E6/$F$1))</f>
         <v>0.61710711402488794</v>
       </c>
@@ -2427,7 +2412,7 @@
         <f t="shared" ref="E7:E8" si="1">D7-$B$2</f>
         <v>-600000</v>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="46">
         <f t="shared" ref="F7:F8" si="2">1-EXP(-(E7/$F$1))</f>
         <v>-0.12749685157937574</v>
       </c>
@@ -2450,7 +2435,7 @@
         <f t="shared" si="1"/>
         <v>-4380000</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="46">
         <f t="shared" si="2"/>
         <v>-1.4012753690986246</v>
       </c>
@@ -2573,28 +2558,28 @@
       <c r="K2" s="37">
         <v>120</v>
       </c>
-      <c r="L2" s="38">
+      <c r="L2" s="37">
         <v>80</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M2" s="37">
         <v>300</v>
       </c>
-      <c r="N2" s="38">
-        <v>0</v>
-      </c>
-      <c r="O2" s="38">
-        <v>0</v>
-      </c>
-      <c r="P2" s="38">
+      <c r="N2" s="37">
+        <v>0</v>
+      </c>
+      <c r="O2" s="37">
+        <v>0</v>
+      </c>
+      <c r="P2" s="37">
         <v>100</v>
       </c>
-      <c r="Q2" s="38">
-        <v>0</v>
-      </c>
-      <c r="R2" s="38">
+      <c r="Q2" s="37">
+        <v>0</v>
+      </c>
+      <c r="R2" s="37">
         <v>6000</v>
       </c>
-      <c r="S2" s="39">
+      <c r="S2" s="37">
         <v>0</v>
       </c>
     </row>
@@ -3241,67 +3226,67 @@
       <c r="J5" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="K5" s="84">
-        <v>0</v>
-      </c>
-      <c r="L5" s="41">
-        <v>0</v>
-      </c>
-      <c r="M5" s="41">
-        <v>0</v>
-      </c>
-      <c r="N5" s="84">
-        <v>0</v>
-      </c>
-      <c r="O5" s="41">
-        <v>0</v>
-      </c>
-      <c r="P5" s="41">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="41">
-        <v>0</v>
-      </c>
-      <c r="R5" s="41">
-        <v>0</v>
-      </c>
-      <c r="S5" s="85">
-        <v>0</v>
-      </c>
-      <c r="T5" s="84">
-        <v>0</v>
-      </c>
-      <c r="U5" s="41">
-        <v>0</v>
-      </c>
-      <c r="V5" s="41">
-        <v>0</v>
-      </c>
-      <c r="W5" s="41">
-        <v>0</v>
-      </c>
-      <c r="X5" s="41">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="85">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="84">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="41">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="41">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="41">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="41">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="85">
+      <c r="K5" s="82">
+        <v>0</v>
+      </c>
+      <c r="L5" s="39">
+        <v>0</v>
+      </c>
+      <c r="M5" s="39">
+        <v>0</v>
+      </c>
+      <c r="N5" s="82">
+        <v>0</v>
+      </c>
+      <c r="O5" s="39">
+        <v>0</v>
+      </c>
+      <c r="P5" s="39">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="39">
+        <v>0</v>
+      </c>
+      <c r="R5" s="39">
+        <v>0</v>
+      </c>
+      <c r="S5" s="83">
+        <v>0</v>
+      </c>
+      <c r="T5" s="82">
+        <v>0</v>
+      </c>
+      <c r="U5" s="39">
+        <v>0</v>
+      </c>
+      <c r="V5" s="39">
+        <v>0</v>
+      </c>
+      <c r="W5" s="39">
+        <v>0</v>
+      </c>
+      <c r="X5" s="39">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="83">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="82">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="39">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="39">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="39">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="39">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="83">
         <v>0</v>
       </c>
     </row>
@@ -3481,7 +3466,7 @@
         <f>D2*E7-D3</f>
         <v>-60</v>
       </c>
-      <c r="I8" s="88" t="s">
+      <c r="I8" s="89" t="s">
         <v>100</v>
       </c>
       <c r="J8" s="21" t="s">
@@ -3554,7 +3539,7 @@
       <c r="E9" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="89"/>
+      <c r="I9" s="90"/>
       <c r="J9" t="s">
         <v>38</v>
       </c>
@@ -3603,7 +3588,7 @@
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I10" s="89"/>
+      <c r="I10" s="90"/>
       <c r="J10" t="s">
         <v>62</v>
       </c>
@@ -3652,7 +3637,7 @@
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I11" s="90"/>
+      <c r="I11" s="91"/>
       <c r="J11" s="26" t="s">
         <v>63</v>
       </c>
@@ -3707,7 +3692,7 @@
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I12" s="91" t="s">
+      <c r="I12" s="92" t="s">
         <v>85</v>
       </c>
       <c r="J12" s="21" t="s">
@@ -3764,7 +3749,7 @@
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I13" s="89"/>
+      <c r="I13" s="90"/>
       <c r="J13" t="s">
         <v>38</v>
       </c>
@@ -3811,7 +3796,7 @@
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I14" s="89"/>
+      <c r="I14" s="90"/>
       <c r="J14" t="s">
         <v>62</v>
       </c>
@@ -3858,7 +3843,7 @@
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I15" s="90"/>
+      <c r="I15" s="91"/>
       <c r="J15" s="26" t="s">
         <v>63</v>
       </c>
@@ -3913,7 +3898,7 @@
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I16" s="91" t="s">
+      <c r="I16" s="92" t="s">
         <v>88</v>
       </c>
       <c r="J16" s="21" t="s">
@@ -3971,7 +3956,7 @@
       </c>
     </row>
     <row r="17" spans="9:34" x14ac:dyDescent="0.35">
-      <c r="I17" s="89"/>
+      <c r="I17" s="90"/>
       <c r="J17" t="s">
         <v>38</v>
       </c>
@@ -4019,7 +4004,7 @@
       </c>
     </row>
     <row r="18" spans="9:34" x14ac:dyDescent="0.35">
-      <c r="I18" s="89"/>
+      <c r="I18" s="90"/>
       <c r="J18" t="s">
         <v>62</v>
       </c>
@@ -4067,7 +4052,7 @@
       </c>
     </row>
     <row r="19" spans="9:34" x14ac:dyDescent="0.35">
-      <c r="I19" s="90"/>
+      <c r="I19" s="91"/>
       <c r="J19" s="26" t="s">
         <v>63</v>
       </c>
@@ -4159,16 +4144,16 @@
       <c r="A2" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="41">
-        <v>0</v>
-      </c>
-      <c r="C2" s="42">
+      <c r="B2" s="39">
+        <v>0</v>
+      </c>
+      <c r="C2" s="40">
         <v>438.78894251864858</v>
       </c>
-      <c r="D2" s="42">
+      <c r="D2" s="40">
         <v>17.551557700745942</v>
       </c>
-      <c r="E2" s="41">
+      <c r="E2" s="39">
         <v>0</v>
       </c>
     </row>
@@ -4188,7 +4173,7 @@
       <c r="E3">
         <v>-6100</v>
       </c>
-      <c r="F3" s="43">
+      <c r="F3" s="41">
         <f>SUMPRODUCT($B$2:$E$2,B3:E3)</f>
         <v>-8819.6577446248266</v>
       </c>
@@ -4216,7 +4201,7 @@
       <c r="G4" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="H4" s="40">
+      <c r="H4" s="38">
         <v>0</v>
       </c>
     </row>
@@ -4243,7 +4228,7 @@
       <c r="G5" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="40">
+      <c r="H5" s="38">
         <v>1000</v>
       </c>
     </row>
@@ -4270,7 +4255,7 @@
       <c r="G6" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="H6" s="40">
+      <c r="H6" s="38">
         <v>2000</v>
       </c>
     </row>
@@ -4297,7 +4282,7 @@
       <c r="G7" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="H7" s="40">
+      <c r="H7" s="38">
         <v>800</v>
       </c>
     </row>
@@ -4324,7 +4309,7 @@
       <c r="G8" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="40">
+      <c r="H8" s="38">
         <v>100000</v>
       </c>
     </row>
@@ -4414,16 +4399,16 @@
       <c r="A6" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="39">
         <v>820.58748569368015</v>
       </c>
-      <c r="C6" s="42">
+      <c r="C6" s="40">
         <v>28.576766199484577</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="40">
         <v>17.469651234835069</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="39">
         <v>0</v>
       </c>
     </row>
@@ -4443,7 +4428,7 @@
       <c r="E7">
         <v>-6100</v>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="42">
         <f>SUMPRODUCT($B$6:$E$6,B7:E7)</f>
         <v>-8311.8376589478867</v>
       </c>
@@ -4469,10 +4454,10 @@
         <f>SUMPRODUCT($B$6:$E$6,B8:E8)</f>
         <v>849.16425189316476</v>
       </c>
-      <c r="G8" s="45" t="s">
+      <c r="G8" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="40">
+      <c r="H8" s="38">
         <v>1000</v>
       </c>
     </row>
@@ -4496,10 +4481,10 @@
         <f>SUMPRODUCT($B$6:$E$6,B9:E9)</f>
         <v>1572.2686111351563</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="H9" s="40">
+      <c r="H9" s="38">
         <v>2000</v>
       </c>
     </row>
@@ -4523,10 +4508,10 @@
         <f>SUMPRODUCT($B$6:$E$6,B10:E10)</f>
         <v>698.78604939340278</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="G10" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="40">
+      <c r="H10" s="38">
         <v>800</v>
       </c>
     </row>
@@ -4550,10 +4535,10 @@
         <f>SUMPRODUCT($B$6:$E$6,B11:E11)</f>
         <v>99999.999997029547</v>
       </c>
-      <c r="G11" s="45" t="s">
+      <c r="G11" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="38">
         <v>100000</v>
       </c>
     </row>
@@ -4561,14 +4546,14 @@
       <c r="A12" t="s">
         <v>118</v>
       </c>
-      <c r="F12" s="46">
+      <c r="F12" s="44">
         <f>SUMPRODUCT(B6:E6,B1:E1)+SQRT(SUMSQ(B3:E3))</f>
         <v>7.3442297176817828E-6</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="G12" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="H12" s="40">
+      <c r="H12" s="38">
         <v>0</v>
       </c>
     </row>
@@ -4627,7 +4612,7 @@
         <f>$I$2</f>
         <v>600</v>
       </c>
-      <c r="D2" s="82">
+      <c r="D2" s="80">
         <f t="shared" ref="D2:D16" si="0">VLOOKUP(B2,$F$2:$G$6,2,FALSE)*VLOOKUP(C2,$I$2:$J$4,2,FALSE)</f>
         <v>1.6500000000000001E-2</v>
       </c>
@@ -4656,7 +4641,7 @@
         <f>$I$2</f>
         <v>600</v>
       </c>
-      <c r="D3" s="82">
+      <c r="D3" s="80">
         <f t="shared" si="0"/>
         <v>6.6000000000000003E-2</v>
       </c>
@@ -4685,7 +4670,7 @@
         <f>$I$2</f>
         <v>600</v>
       </c>
-      <c r="D4" s="82">
+      <c r="D4" s="80">
         <f t="shared" si="0"/>
         <v>6.6000000000000003E-2</v>
       </c>
@@ -4714,7 +4699,7 @@
         <f>$I$2</f>
         <v>600</v>
       </c>
-      <c r="D5" s="82">
+      <c r="D5" s="80">
         <f t="shared" si="0"/>
         <v>8.2500000000000004E-2</v>
       </c>
@@ -4744,7 +4729,7 @@
         <f>$I$2</f>
         <v>600</v>
       </c>
-      <c r="D6" s="82">
+      <c r="D6" s="80">
         <f t="shared" si="0"/>
         <v>9.9000000000000005E-2</v>
       </c>
@@ -4767,7 +4752,7 @@
         <f>$I$3</f>
         <v>1200</v>
       </c>
-      <c r="D7" s="82">
+      <c r="D7" s="80">
         <f t="shared" si="0"/>
         <v>1.7000000000000001E-2</v>
       </c>
@@ -4791,7 +4776,7 @@
         <f>$I$3</f>
         <v>1200</v>
       </c>
-      <c r="D8" s="82">
+      <c r="D8" s="80">
         <f t="shared" si="0"/>
         <v>6.8000000000000005E-2</v>
       </c>
@@ -4808,7 +4793,7 @@
         <f>$I$3</f>
         <v>1200</v>
       </c>
-      <c r="D9" s="82">
+      <c r="D9" s="80">
         <f t="shared" si="0"/>
         <v>6.8000000000000005E-2</v>
       </c>
@@ -4825,7 +4810,7 @@
         <f>$I$3</f>
         <v>1200</v>
       </c>
-      <c r="D10" s="82">
+      <c r="D10" s="80">
         <f t="shared" si="0"/>
         <v>8.5000000000000006E-2</v>
       </c>
@@ -4842,7 +4827,7 @@
         <f>$I$3</f>
         <v>1200</v>
       </c>
-      <c r="D11" s="82">
+      <c r="D11" s="80">
         <f t="shared" si="0"/>
         <v>0.10200000000000001</v>
       </c>
@@ -4859,7 +4844,7 @@
         <f>$I$4</f>
         <v>1800</v>
       </c>
-      <c r="D12" s="82">
+      <c r="D12" s="80">
         <f t="shared" si="0"/>
         <v>1.6500000000000001E-2</v>
       </c>
@@ -4876,7 +4861,7 @@
         <f>$I$4</f>
         <v>1800</v>
       </c>
-      <c r="D13" s="82">
+      <c r="D13" s="80">
         <f t="shared" si="0"/>
         <v>6.6000000000000003E-2</v>
       </c>
@@ -4893,7 +4878,7 @@
         <f>$I$4</f>
         <v>1800</v>
       </c>
-      <c r="D14" s="82">
+      <c r="D14" s="80">
         <f t="shared" si="0"/>
         <v>6.6000000000000003E-2</v>
       </c>
@@ -4910,7 +4895,7 @@
         <f>$I$4</f>
         <v>1800</v>
       </c>
-      <c r="D15" s="82">
+      <c r="D15" s="80">
         <f t="shared" si="0"/>
         <v>8.2500000000000004E-2</v>
       </c>
@@ -4927,7 +4912,7 @@
         <f>$I$4</f>
         <v>1800</v>
       </c>
-      <c r="D16" s="82">
+      <c r="D16" s="80">
         <f t="shared" si="0"/>
         <v>9.9000000000000005E-2</v>
       </c>
@@ -4936,7 +4921,7 @@
       <c r="A17" t="s">
         <v>179</v>
       </c>
-      <c r="D17" s="82">
+      <c r="D17" s="80">
         <f>SUM(D2:D16)</f>
         <v>1</v>
       </c>
@@ -4956,7 +4941,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="13.9" x14ac:dyDescent="0.4">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="47" t="s">
         <v>132</v>
       </c>
       <c r="F1">
@@ -4971,12 +4956,12 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="13.9" x14ac:dyDescent="0.4">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="47" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="13.9" x14ac:dyDescent="0.4">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="47" t="s">
         <v>134</v>
       </c>
     </row>
@@ -4995,25 +4980,25 @@
       <c r="A7" t="s">
         <v>137</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="D7" s="50"/>
+      <c r="B7" s="46"/>
+      <c r="D7" s="48"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>138</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="D8" s="50"/>
+      <c r="B8" s="46"/>
+      <c r="D8" s="48"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>139</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="D9" s="50"/>
+      <c r="B9" s="46"/>
+      <c r="D9" s="48"/>
     </row>
     <row r="11" spans="1:6" ht="13.9" x14ac:dyDescent="0.4">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="47" t="s">
         <v>140</v>
       </c>
     </row>
@@ -5022,24 +5007,24 @@
         <v>141</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="D12" s="51"/>
+      <c r="D12" s="49"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>142</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="D13" s="51"/>
+      <c r="D13" s="49"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>143</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="D14" s="51"/>
+      <c r="D14" s="49"/>
     </row>
     <row r="16" spans="1:6" ht="13.9" x14ac:dyDescent="0.4">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="47" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5047,7 +5032,7 @@
       <c r="A18" t="s">
         <v>123</v>
       </c>
-      <c r="B18" s="52">
+      <c r="B18" s="50">
         <v>75</v>
       </c>
       <c r="C18" t="s">
@@ -5058,7 +5043,7 @@
       <c r="A19" t="s">
         <v>145</v>
       </c>
-      <c r="B19" s="52">
+      <c r="B19" s="50">
         <v>8</v>
       </c>
       <c r="C19" t="s">
@@ -5066,7 +5051,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="13.9" x14ac:dyDescent="0.4">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="47" t="s">
         <v>134</v>
       </c>
     </row>
@@ -5085,11 +5070,11 @@
       <c r="A23" t="s">
         <v>146</v>
       </c>
-      <c r="B23" s="48">
+      <c r="B23" s="46">
         <f>_xlfn.NORM.DIST(80,$B$18,$B$19,TRUE)</f>
         <v>0.73401447095129946</v>
       </c>
-      <c r="D23" s="53"/>
+      <c r="D23" s="51"/>
       <c r="E23" t="s">
         <v>218</v>
       </c>
@@ -5098,18 +5083,18 @@
       <c r="A24" t="s">
         <v>147</v>
       </c>
-      <c r="B24" s="48"/>
-      <c r="D24" s="53"/>
+      <c r="B24" s="46"/>
+      <c r="D24" s="51"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>148</v>
       </c>
-      <c r="B25" s="48"/>
-      <c r="D25" s="53"/>
+      <c r="B25" s="46"/>
+      <c r="D25" s="51"/>
     </row>
     <row r="27" spans="1:5" ht="13.9" x14ac:dyDescent="0.4">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="47" t="s">
         <v>140</v>
       </c>
     </row>
@@ -5118,14 +5103,14 @@
         <v>141</v>
       </c>
       <c r="B28" s="3"/>
-      <c r="D28" s="51"/>
+      <c r="D28" s="49"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>149</v>
       </c>
       <c r="B29" s="3"/>
-      <c r="D29" s="51"/>
+      <c r="D29" s="49"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
@@ -5135,7 +5120,7 @@
         <f>_xlfn.NORM.INV(0.97,$B$18,$B$19)</f>
         <v>90.046348865210007</v>
       </c>
-      <c r="D30" s="51"/>
+      <c r="D30" s="49"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
@@ -5179,7 +5164,7 @@
       <c r="A39" t="s">
         <v>224</v>
       </c>
-      <c r="B39" s="41">
+      <c r="B39" s="39">
         <f>_xlfn.NORM.DIST(B38,B36,B37, TRUE)</f>
         <v>0.79767161903635697</v>
       </c>
@@ -5219,7 +5204,7 @@
       <c r="F1" t="s">
         <v>154</v>
       </c>
-      <c r="L1" s="56" t="s">
+      <c r="L1" s="54" t="s">
         <v>203</v>
       </c>
     </row>
@@ -5280,7 +5265,7 @@
       <c r="P3" t="s">
         <v>208</v>
       </c>
-      <c r="S3" s="86" t="s">
+      <c r="S3" s="84" t="s">
         <v>205</v>
       </c>
       <c r="T3" t="s">
@@ -5423,7 +5408,7 @@
         <f>SUM(N4:P4)</f>
         <v>38</v>
       </c>
-      <c r="S8" s="93" t="s">
+      <c r="S8" s="85" t="s">
         <v>214</v>
       </c>
       <c r="T8" s="31" cm="1">
@@ -5477,7 +5462,6 @@
       <c r="L12" t="s">
         <v>215</v>
       </c>
-      <c r="M12" s="92"/>
       <c r="N12" s="31">
         <f>N5</f>
         <v>2</v>
@@ -5496,7 +5480,6 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="M13" s="92"/>
       <c r="N13" s="31">
         <v>0</v>
       </c>
@@ -5512,7 +5495,6 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="M14" s="92"/>
       <c r="N14" s="31">
         <v>0</v>
       </c>
@@ -5528,7 +5510,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="R16" s="94" t="s">
+      <c r="R16" t="s">
         <v>227</v>
       </c>
       <c r="S16" s="12" t="s">
@@ -5558,557 +5540,557 @@
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.875" style="58" customWidth="1"/>
-    <col min="2" max="5" width="16.875" style="58" customWidth="1"/>
-    <col min="6" max="6" width="17.875" style="58" customWidth="1"/>
-    <col min="7" max="7" width="11.5625" style="58" customWidth="1"/>
-    <col min="8" max="256" width="8.875" style="58"/>
-    <col min="257" max="257" width="21.875" style="58" customWidth="1"/>
-    <col min="258" max="261" width="16.875" style="58" customWidth="1"/>
-    <col min="262" max="262" width="17.875" style="58" customWidth="1"/>
-    <col min="263" max="263" width="11.5625" style="58" customWidth="1"/>
-    <col min="264" max="512" width="8.875" style="58"/>
-    <col min="513" max="513" width="21.875" style="58" customWidth="1"/>
-    <col min="514" max="517" width="16.875" style="58" customWidth="1"/>
-    <col min="518" max="518" width="17.875" style="58" customWidth="1"/>
-    <col min="519" max="519" width="11.5625" style="58" customWidth="1"/>
-    <col min="520" max="768" width="8.875" style="58"/>
-    <col min="769" max="769" width="21.875" style="58" customWidth="1"/>
-    <col min="770" max="773" width="16.875" style="58" customWidth="1"/>
-    <col min="774" max="774" width="17.875" style="58" customWidth="1"/>
-    <col min="775" max="775" width="11.5625" style="58" customWidth="1"/>
-    <col min="776" max="1024" width="8.875" style="58"/>
-    <col min="1025" max="1025" width="21.875" style="58" customWidth="1"/>
-    <col min="1026" max="1029" width="16.875" style="58" customWidth="1"/>
-    <col min="1030" max="1030" width="17.875" style="58" customWidth="1"/>
-    <col min="1031" max="1031" width="11.5625" style="58" customWidth="1"/>
-    <col min="1032" max="1280" width="8.875" style="58"/>
-    <col min="1281" max="1281" width="21.875" style="58" customWidth="1"/>
-    <col min="1282" max="1285" width="16.875" style="58" customWidth="1"/>
-    <col min="1286" max="1286" width="17.875" style="58" customWidth="1"/>
-    <col min="1287" max="1287" width="11.5625" style="58" customWidth="1"/>
-    <col min="1288" max="1536" width="8.875" style="58"/>
-    <col min="1537" max="1537" width="21.875" style="58" customWidth="1"/>
-    <col min="1538" max="1541" width="16.875" style="58" customWidth="1"/>
-    <col min="1542" max="1542" width="17.875" style="58" customWidth="1"/>
-    <col min="1543" max="1543" width="11.5625" style="58" customWidth="1"/>
-    <col min="1544" max="1792" width="8.875" style="58"/>
-    <col min="1793" max="1793" width="21.875" style="58" customWidth="1"/>
-    <col min="1794" max="1797" width="16.875" style="58" customWidth="1"/>
-    <col min="1798" max="1798" width="17.875" style="58" customWidth="1"/>
-    <col min="1799" max="1799" width="11.5625" style="58" customWidth="1"/>
-    <col min="1800" max="2048" width="8.875" style="58"/>
-    <col min="2049" max="2049" width="21.875" style="58" customWidth="1"/>
-    <col min="2050" max="2053" width="16.875" style="58" customWidth="1"/>
-    <col min="2054" max="2054" width="17.875" style="58" customWidth="1"/>
-    <col min="2055" max="2055" width="11.5625" style="58" customWidth="1"/>
-    <col min="2056" max="2304" width="8.875" style="58"/>
-    <col min="2305" max="2305" width="21.875" style="58" customWidth="1"/>
-    <col min="2306" max="2309" width="16.875" style="58" customWidth="1"/>
-    <col min="2310" max="2310" width="17.875" style="58" customWidth="1"/>
-    <col min="2311" max="2311" width="11.5625" style="58" customWidth="1"/>
-    <col min="2312" max="2560" width="8.875" style="58"/>
-    <col min="2561" max="2561" width="21.875" style="58" customWidth="1"/>
-    <col min="2562" max="2565" width="16.875" style="58" customWidth="1"/>
-    <col min="2566" max="2566" width="17.875" style="58" customWidth="1"/>
-    <col min="2567" max="2567" width="11.5625" style="58" customWidth="1"/>
-    <col min="2568" max="2816" width="8.875" style="58"/>
-    <col min="2817" max="2817" width="21.875" style="58" customWidth="1"/>
-    <col min="2818" max="2821" width="16.875" style="58" customWidth="1"/>
-    <col min="2822" max="2822" width="17.875" style="58" customWidth="1"/>
-    <col min="2823" max="2823" width="11.5625" style="58" customWidth="1"/>
-    <col min="2824" max="3072" width="8.875" style="58"/>
-    <col min="3073" max="3073" width="21.875" style="58" customWidth="1"/>
-    <col min="3074" max="3077" width="16.875" style="58" customWidth="1"/>
-    <col min="3078" max="3078" width="17.875" style="58" customWidth="1"/>
-    <col min="3079" max="3079" width="11.5625" style="58" customWidth="1"/>
-    <col min="3080" max="3328" width="8.875" style="58"/>
-    <col min="3329" max="3329" width="21.875" style="58" customWidth="1"/>
-    <col min="3330" max="3333" width="16.875" style="58" customWidth="1"/>
-    <col min="3334" max="3334" width="17.875" style="58" customWidth="1"/>
-    <col min="3335" max="3335" width="11.5625" style="58" customWidth="1"/>
-    <col min="3336" max="3584" width="8.875" style="58"/>
-    <col min="3585" max="3585" width="21.875" style="58" customWidth="1"/>
-    <col min="3586" max="3589" width="16.875" style="58" customWidth="1"/>
-    <col min="3590" max="3590" width="17.875" style="58" customWidth="1"/>
-    <col min="3591" max="3591" width="11.5625" style="58" customWidth="1"/>
-    <col min="3592" max="3840" width="8.875" style="58"/>
-    <col min="3841" max="3841" width="21.875" style="58" customWidth="1"/>
-    <col min="3842" max="3845" width="16.875" style="58" customWidth="1"/>
-    <col min="3846" max="3846" width="17.875" style="58" customWidth="1"/>
-    <col min="3847" max="3847" width="11.5625" style="58" customWidth="1"/>
-    <col min="3848" max="4096" width="8.875" style="58"/>
-    <col min="4097" max="4097" width="21.875" style="58" customWidth="1"/>
-    <col min="4098" max="4101" width="16.875" style="58" customWidth="1"/>
-    <col min="4102" max="4102" width="17.875" style="58" customWidth="1"/>
-    <col min="4103" max="4103" width="11.5625" style="58" customWidth="1"/>
-    <col min="4104" max="4352" width="8.875" style="58"/>
-    <col min="4353" max="4353" width="21.875" style="58" customWidth="1"/>
-    <col min="4354" max="4357" width="16.875" style="58" customWidth="1"/>
-    <col min="4358" max="4358" width="17.875" style="58" customWidth="1"/>
-    <col min="4359" max="4359" width="11.5625" style="58" customWidth="1"/>
-    <col min="4360" max="4608" width="8.875" style="58"/>
-    <col min="4609" max="4609" width="21.875" style="58" customWidth="1"/>
-    <col min="4610" max="4613" width="16.875" style="58" customWidth="1"/>
-    <col min="4614" max="4614" width="17.875" style="58" customWidth="1"/>
-    <col min="4615" max="4615" width="11.5625" style="58" customWidth="1"/>
-    <col min="4616" max="4864" width="8.875" style="58"/>
-    <col min="4865" max="4865" width="21.875" style="58" customWidth="1"/>
-    <col min="4866" max="4869" width="16.875" style="58" customWidth="1"/>
-    <col min="4870" max="4870" width="17.875" style="58" customWidth="1"/>
-    <col min="4871" max="4871" width="11.5625" style="58" customWidth="1"/>
-    <col min="4872" max="5120" width="8.875" style="58"/>
-    <col min="5121" max="5121" width="21.875" style="58" customWidth="1"/>
-    <col min="5122" max="5125" width="16.875" style="58" customWidth="1"/>
-    <col min="5126" max="5126" width="17.875" style="58" customWidth="1"/>
-    <col min="5127" max="5127" width="11.5625" style="58" customWidth="1"/>
-    <col min="5128" max="5376" width="8.875" style="58"/>
-    <col min="5377" max="5377" width="21.875" style="58" customWidth="1"/>
-    <col min="5378" max="5381" width="16.875" style="58" customWidth="1"/>
-    <col min="5382" max="5382" width="17.875" style="58" customWidth="1"/>
-    <col min="5383" max="5383" width="11.5625" style="58" customWidth="1"/>
-    <col min="5384" max="5632" width="8.875" style="58"/>
-    <col min="5633" max="5633" width="21.875" style="58" customWidth="1"/>
-    <col min="5634" max="5637" width="16.875" style="58" customWidth="1"/>
-    <col min="5638" max="5638" width="17.875" style="58" customWidth="1"/>
-    <col min="5639" max="5639" width="11.5625" style="58" customWidth="1"/>
-    <col min="5640" max="5888" width="8.875" style="58"/>
-    <col min="5889" max="5889" width="21.875" style="58" customWidth="1"/>
-    <col min="5890" max="5893" width="16.875" style="58" customWidth="1"/>
-    <col min="5894" max="5894" width="17.875" style="58" customWidth="1"/>
-    <col min="5895" max="5895" width="11.5625" style="58" customWidth="1"/>
-    <col min="5896" max="6144" width="8.875" style="58"/>
-    <col min="6145" max="6145" width="21.875" style="58" customWidth="1"/>
-    <col min="6146" max="6149" width="16.875" style="58" customWidth="1"/>
-    <col min="6150" max="6150" width="17.875" style="58" customWidth="1"/>
-    <col min="6151" max="6151" width="11.5625" style="58" customWidth="1"/>
-    <col min="6152" max="6400" width="8.875" style="58"/>
-    <col min="6401" max="6401" width="21.875" style="58" customWidth="1"/>
-    <col min="6402" max="6405" width="16.875" style="58" customWidth="1"/>
-    <col min="6406" max="6406" width="17.875" style="58" customWidth="1"/>
-    <col min="6407" max="6407" width="11.5625" style="58" customWidth="1"/>
-    <col min="6408" max="6656" width="8.875" style="58"/>
-    <col min="6657" max="6657" width="21.875" style="58" customWidth="1"/>
-    <col min="6658" max="6661" width="16.875" style="58" customWidth="1"/>
-    <col min="6662" max="6662" width="17.875" style="58" customWidth="1"/>
-    <col min="6663" max="6663" width="11.5625" style="58" customWidth="1"/>
-    <col min="6664" max="6912" width="8.875" style="58"/>
-    <col min="6913" max="6913" width="21.875" style="58" customWidth="1"/>
-    <col min="6914" max="6917" width="16.875" style="58" customWidth="1"/>
-    <col min="6918" max="6918" width="17.875" style="58" customWidth="1"/>
-    <col min="6919" max="6919" width="11.5625" style="58" customWidth="1"/>
-    <col min="6920" max="7168" width="8.875" style="58"/>
-    <col min="7169" max="7169" width="21.875" style="58" customWidth="1"/>
-    <col min="7170" max="7173" width="16.875" style="58" customWidth="1"/>
-    <col min="7174" max="7174" width="17.875" style="58" customWidth="1"/>
-    <col min="7175" max="7175" width="11.5625" style="58" customWidth="1"/>
-    <col min="7176" max="7424" width="8.875" style="58"/>
-    <col min="7425" max="7425" width="21.875" style="58" customWidth="1"/>
-    <col min="7426" max="7429" width="16.875" style="58" customWidth="1"/>
-    <col min="7430" max="7430" width="17.875" style="58" customWidth="1"/>
-    <col min="7431" max="7431" width="11.5625" style="58" customWidth="1"/>
-    <col min="7432" max="7680" width="8.875" style="58"/>
-    <col min="7681" max="7681" width="21.875" style="58" customWidth="1"/>
-    <col min="7682" max="7685" width="16.875" style="58" customWidth="1"/>
-    <col min="7686" max="7686" width="17.875" style="58" customWidth="1"/>
-    <col min="7687" max="7687" width="11.5625" style="58" customWidth="1"/>
-    <col min="7688" max="7936" width="8.875" style="58"/>
-    <col min="7937" max="7937" width="21.875" style="58" customWidth="1"/>
-    <col min="7938" max="7941" width="16.875" style="58" customWidth="1"/>
-    <col min="7942" max="7942" width="17.875" style="58" customWidth="1"/>
-    <col min="7943" max="7943" width="11.5625" style="58" customWidth="1"/>
-    <col min="7944" max="8192" width="8.875" style="58"/>
-    <col min="8193" max="8193" width="21.875" style="58" customWidth="1"/>
-    <col min="8194" max="8197" width="16.875" style="58" customWidth="1"/>
-    <col min="8198" max="8198" width="17.875" style="58" customWidth="1"/>
-    <col min="8199" max="8199" width="11.5625" style="58" customWidth="1"/>
-    <col min="8200" max="8448" width="8.875" style="58"/>
-    <col min="8449" max="8449" width="21.875" style="58" customWidth="1"/>
-    <col min="8450" max="8453" width="16.875" style="58" customWidth="1"/>
-    <col min="8454" max="8454" width="17.875" style="58" customWidth="1"/>
-    <col min="8455" max="8455" width="11.5625" style="58" customWidth="1"/>
-    <col min="8456" max="8704" width="8.875" style="58"/>
-    <col min="8705" max="8705" width="21.875" style="58" customWidth="1"/>
-    <col min="8706" max="8709" width="16.875" style="58" customWidth="1"/>
-    <col min="8710" max="8710" width="17.875" style="58" customWidth="1"/>
-    <col min="8711" max="8711" width="11.5625" style="58" customWidth="1"/>
-    <col min="8712" max="8960" width="8.875" style="58"/>
-    <col min="8961" max="8961" width="21.875" style="58" customWidth="1"/>
-    <col min="8962" max="8965" width="16.875" style="58" customWidth="1"/>
-    <col min="8966" max="8966" width="17.875" style="58" customWidth="1"/>
-    <col min="8967" max="8967" width="11.5625" style="58" customWidth="1"/>
-    <col min="8968" max="9216" width="8.875" style="58"/>
-    <col min="9217" max="9217" width="21.875" style="58" customWidth="1"/>
-    <col min="9218" max="9221" width="16.875" style="58" customWidth="1"/>
-    <col min="9222" max="9222" width="17.875" style="58" customWidth="1"/>
-    <col min="9223" max="9223" width="11.5625" style="58" customWidth="1"/>
-    <col min="9224" max="9472" width="8.875" style="58"/>
-    <col min="9473" max="9473" width="21.875" style="58" customWidth="1"/>
-    <col min="9474" max="9477" width="16.875" style="58" customWidth="1"/>
-    <col min="9478" max="9478" width="17.875" style="58" customWidth="1"/>
-    <col min="9479" max="9479" width="11.5625" style="58" customWidth="1"/>
-    <col min="9480" max="9728" width="8.875" style="58"/>
-    <col min="9729" max="9729" width="21.875" style="58" customWidth="1"/>
-    <col min="9730" max="9733" width="16.875" style="58" customWidth="1"/>
-    <col min="9734" max="9734" width="17.875" style="58" customWidth="1"/>
-    <col min="9735" max="9735" width="11.5625" style="58" customWidth="1"/>
-    <col min="9736" max="9984" width="8.875" style="58"/>
-    <col min="9985" max="9985" width="21.875" style="58" customWidth="1"/>
-    <col min="9986" max="9989" width="16.875" style="58" customWidth="1"/>
-    <col min="9990" max="9990" width="17.875" style="58" customWidth="1"/>
-    <col min="9991" max="9991" width="11.5625" style="58" customWidth="1"/>
-    <col min="9992" max="10240" width="8.875" style="58"/>
-    <col min="10241" max="10241" width="21.875" style="58" customWidth="1"/>
-    <col min="10242" max="10245" width="16.875" style="58" customWidth="1"/>
-    <col min="10246" max="10246" width="17.875" style="58" customWidth="1"/>
-    <col min="10247" max="10247" width="11.5625" style="58" customWidth="1"/>
-    <col min="10248" max="10496" width="8.875" style="58"/>
-    <col min="10497" max="10497" width="21.875" style="58" customWidth="1"/>
-    <col min="10498" max="10501" width="16.875" style="58" customWidth="1"/>
-    <col min="10502" max="10502" width="17.875" style="58" customWidth="1"/>
-    <col min="10503" max="10503" width="11.5625" style="58" customWidth="1"/>
-    <col min="10504" max="10752" width="8.875" style="58"/>
-    <col min="10753" max="10753" width="21.875" style="58" customWidth="1"/>
-    <col min="10754" max="10757" width="16.875" style="58" customWidth="1"/>
-    <col min="10758" max="10758" width="17.875" style="58" customWidth="1"/>
-    <col min="10759" max="10759" width="11.5625" style="58" customWidth="1"/>
-    <col min="10760" max="11008" width="8.875" style="58"/>
-    <col min="11009" max="11009" width="21.875" style="58" customWidth="1"/>
-    <col min="11010" max="11013" width="16.875" style="58" customWidth="1"/>
-    <col min="11014" max="11014" width="17.875" style="58" customWidth="1"/>
-    <col min="11015" max="11015" width="11.5625" style="58" customWidth="1"/>
-    <col min="11016" max="11264" width="8.875" style="58"/>
-    <col min="11265" max="11265" width="21.875" style="58" customWidth="1"/>
-    <col min="11266" max="11269" width="16.875" style="58" customWidth="1"/>
-    <col min="11270" max="11270" width="17.875" style="58" customWidth="1"/>
-    <col min="11271" max="11271" width="11.5625" style="58" customWidth="1"/>
-    <col min="11272" max="11520" width="8.875" style="58"/>
-    <col min="11521" max="11521" width="21.875" style="58" customWidth="1"/>
-    <col min="11522" max="11525" width="16.875" style="58" customWidth="1"/>
-    <col min="11526" max="11526" width="17.875" style="58" customWidth="1"/>
-    <col min="11527" max="11527" width="11.5625" style="58" customWidth="1"/>
-    <col min="11528" max="11776" width="8.875" style="58"/>
-    <col min="11777" max="11777" width="21.875" style="58" customWidth="1"/>
-    <col min="11778" max="11781" width="16.875" style="58" customWidth="1"/>
-    <col min="11782" max="11782" width="17.875" style="58" customWidth="1"/>
-    <col min="11783" max="11783" width="11.5625" style="58" customWidth="1"/>
-    <col min="11784" max="12032" width="8.875" style="58"/>
-    <col min="12033" max="12033" width="21.875" style="58" customWidth="1"/>
-    <col min="12034" max="12037" width="16.875" style="58" customWidth="1"/>
-    <col min="12038" max="12038" width="17.875" style="58" customWidth="1"/>
-    <col min="12039" max="12039" width="11.5625" style="58" customWidth="1"/>
-    <col min="12040" max="12288" width="8.875" style="58"/>
-    <col min="12289" max="12289" width="21.875" style="58" customWidth="1"/>
-    <col min="12290" max="12293" width="16.875" style="58" customWidth="1"/>
-    <col min="12294" max="12294" width="17.875" style="58" customWidth="1"/>
-    <col min="12295" max="12295" width="11.5625" style="58" customWidth="1"/>
-    <col min="12296" max="12544" width="8.875" style="58"/>
-    <col min="12545" max="12545" width="21.875" style="58" customWidth="1"/>
-    <col min="12546" max="12549" width="16.875" style="58" customWidth="1"/>
-    <col min="12550" max="12550" width="17.875" style="58" customWidth="1"/>
-    <col min="12551" max="12551" width="11.5625" style="58" customWidth="1"/>
-    <col min="12552" max="12800" width="8.875" style="58"/>
-    <col min="12801" max="12801" width="21.875" style="58" customWidth="1"/>
-    <col min="12802" max="12805" width="16.875" style="58" customWidth="1"/>
-    <col min="12806" max="12806" width="17.875" style="58" customWidth="1"/>
-    <col min="12807" max="12807" width="11.5625" style="58" customWidth="1"/>
-    <col min="12808" max="13056" width="8.875" style="58"/>
-    <col min="13057" max="13057" width="21.875" style="58" customWidth="1"/>
-    <col min="13058" max="13061" width="16.875" style="58" customWidth="1"/>
-    <col min="13062" max="13062" width="17.875" style="58" customWidth="1"/>
-    <col min="13063" max="13063" width="11.5625" style="58" customWidth="1"/>
-    <col min="13064" max="13312" width="8.875" style="58"/>
-    <col min="13313" max="13313" width="21.875" style="58" customWidth="1"/>
-    <col min="13314" max="13317" width="16.875" style="58" customWidth="1"/>
-    <col min="13318" max="13318" width="17.875" style="58" customWidth="1"/>
-    <col min="13319" max="13319" width="11.5625" style="58" customWidth="1"/>
-    <col min="13320" max="13568" width="8.875" style="58"/>
-    <col min="13569" max="13569" width="21.875" style="58" customWidth="1"/>
-    <col min="13570" max="13573" width="16.875" style="58" customWidth="1"/>
-    <col min="13574" max="13574" width="17.875" style="58" customWidth="1"/>
-    <col min="13575" max="13575" width="11.5625" style="58" customWidth="1"/>
-    <col min="13576" max="13824" width="8.875" style="58"/>
-    <col min="13825" max="13825" width="21.875" style="58" customWidth="1"/>
-    <col min="13826" max="13829" width="16.875" style="58" customWidth="1"/>
-    <col min="13830" max="13830" width="17.875" style="58" customWidth="1"/>
-    <col min="13831" max="13831" width="11.5625" style="58" customWidth="1"/>
-    <col min="13832" max="14080" width="8.875" style="58"/>
-    <col min="14081" max="14081" width="21.875" style="58" customWidth="1"/>
-    <col min="14082" max="14085" width="16.875" style="58" customWidth="1"/>
-    <col min="14086" max="14086" width="17.875" style="58" customWidth="1"/>
-    <col min="14087" max="14087" width="11.5625" style="58" customWidth="1"/>
-    <col min="14088" max="14336" width="8.875" style="58"/>
-    <col min="14337" max="14337" width="21.875" style="58" customWidth="1"/>
-    <col min="14338" max="14341" width="16.875" style="58" customWidth="1"/>
-    <col min="14342" max="14342" width="17.875" style="58" customWidth="1"/>
-    <col min="14343" max="14343" width="11.5625" style="58" customWidth="1"/>
-    <col min="14344" max="14592" width="8.875" style="58"/>
-    <col min="14593" max="14593" width="21.875" style="58" customWidth="1"/>
-    <col min="14594" max="14597" width="16.875" style="58" customWidth="1"/>
-    <col min="14598" max="14598" width="17.875" style="58" customWidth="1"/>
-    <col min="14599" max="14599" width="11.5625" style="58" customWidth="1"/>
-    <col min="14600" max="14848" width="8.875" style="58"/>
-    <col min="14849" max="14849" width="21.875" style="58" customWidth="1"/>
-    <col min="14850" max="14853" width="16.875" style="58" customWidth="1"/>
-    <col min="14854" max="14854" width="17.875" style="58" customWidth="1"/>
-    <col min="14855" max="14855" width="11.5625" style="58" customWidth="1"/>
-    <col min="14856" max="15104" width="8.875" style="58"/>
-    <col min="15105" max="15105" width="21.875" style="58" customWidth="1"/>
-    <col min="15106" max="15109" width="16.875" style="58" customWidth="1"/>
-    <col min="15110" max="15110" width="17.875" style="58" customWidth="1"/>
-    <col min="15111" max="15111" width="11.5625" style="58" customWidth="1"/>
-    <col min="15112" max="15360" width="8.875" style="58"/>
-    <col min="15361" max="15361" width="21.875" style="58" customWidth="1"/>
-    <col min="15362" max="15365" width="16.875" style="58" customWidth="1"/>
-    <col min="15366" max="15366" width="17.875" style="58" customWidth="1"/>
-    <col min="15367" max="15367" width="11.5625" style="58" customWidth="1"/>
-    <col min="15368" max="15616" width="8.875" style="58"/>
-    <col min="15617" max="15617" width="21.875" style="58" customWidth="1"/>
-    <col min="15618" max="15621" width="16.875" style="58" customWidth="1"/>
-    <col min="15622" max="15622" width="17.875" style="58" customWidth="1"/>
-    <col min="15623" max="15623" width="11.5625" style="58" customWidth="1"/>
-    <col min="15624" max="15872" width="8.875" style="58"/>
-    <col min="15873" max="15873" width="21.875" style="58" customWidth="1"/>
-    <col min="15874" max="15877" width="16.875" style="58" customWidth="1"/>
-    <col min="15878" max="15878" width="17.875" style="58" customWidth="1"/>
-    <col min="15879" max="15879" width="11.5625" style="58" customWidth="1"/>
-    <col min="15880" max="16128" width="8.875" style="58"/>
-    <col min="16129" max="16129" width="21.875" style="58" customWidth="1"/>
-    <col min="16130" max="16133" width="16.875" style="58" customWidth="1"/>
-    <col min="16134" max="16134" width="17.875" style="58" customWidth="1"/>
-    <col min="16135" max="16135" width="11.5625" style="58" customWidth="1"/>
-    <col min="16136" max="16384" width="8.875" style="58"/>
+    <col min="1" max="1" width="21.875" style="56" customWidth="1"/>
+    <col min="2" max="5" width="16.875" style="56" customWidth="1"/>
+    <col min="6" max="6" width="17.875" style="56" customWidth="1"/>
+    <col min="7" max="7" width="11.5625" style="56" customWidth="1"/>
+    <col min="8" max="256" width="8.875" style="56"/>
+    <col min="257" max="257" width="21.875" style="56" customWidth="1"/>
+    <col min="258" max="261" width="16.875" style="56" customWidth="1"/>
+    <col min="262" max="262" width="17.875" style="56" customWidth="1"/>
+    <col min="263" max="263" width="11.5625" style="56" customWidth="1"/>
+    <col min="264" max="512" width="8.875" style="56"/>
+    <col min="513" max="513" width="21.875" style="56" customWidth="1"/>
+    <col min="514" max="517" width="16.875" style="56" customWidth="1"/>
+    <col min="518" max="518" width="17.875" style="56" customWidth="1"/>
+    <col min="519" max="519" width="11.5625" style="56" customWidth="1"/>
+    <col min="520" max="768" width="8.875" style="56"/>
+    <col min="769" max="769" width="21.875" style="56" customWidth="1"/>
+    <col min="770" max="773" width="16.875" style="56" customWidth="1"/>
+    <col min="774" max="774" width="17.875" style="56" customWidth="1"/>
+    <col min="775" max="775" width="11.5625" style="56" customWidth="1"/>
+    <col min="776" max="1024" width="8.875" style="56"/>
+    <col min="1025" max="1025" width="21.875" style="56" customWidth="1"/>
+    <col min="1026" max="1029" width="16.875" style="56" customWidth="1"/>
+    <col min="1030" max="1030" width="17.875" style="56" customWidth="1"/>
+    <col min="1031" max="1031" width="11.5625" style="56" customWidth="1"/>
+    <col min="1032" max="1280" width="8.875" style="56"/>
+    <col min="1281" max="1281" width="21.875" style="56" customWidth="1"/>
+    <col min="1282" max="1285" width="16.875" style="56" customWidth="1"/>
+    <col min="1286" max="1286" width="17.875" style="56" customWidth="1"/>
+    <col min="1287" max="1287" width="11.5625" style="56" customWidth="1"/>
+    <col min="1288" max="1536" width="8.875" style="56"/>
+    <col min="1537" max="1537" width="21.875" style="56" customWidth="1"/>
+    <col min="1538" max="1541" width="16.875" style="56" customWidth="1"/>
+    <col min="1542" max="1542" width="17.875" style="56" customWidth="1"/>
+    <col min="1543" max="1543" width="11.5625" style="56" customWidth="1"/>
+    <col min="1544" max="1792" width="8.875" style="56"/>
+    <col min="1793" max="1793" width="21.875" style="56" customWidth="1"/>
+    <col min="1794" max="1797" width="16.875" style="56" customWidth="1"/>
+    <col min="1798" max="1798" width="17.875" style="56" customWidth="1"/>
+    <col min="1799" max="1799" width="11.5625" style="56" customWidth="1"/>
+    <col min="1800" max="2048" width="8.875" style="56"/>
+    <col min="2049" max="2049" width="21.875" style="56" customWidth="1"/>
+    <col min="2050" max="2053" width="16.875" style="56" customWidth="1"/>
+    <col min="2054" max="2054" width="17.875" style="56" customWidth="1"/>
+    <col min="2055" max="2055" width="11.5625" style="56" customWidth="1"/>
+    <col min="2056" max="2304" width="8.875" style="56"/>
+    <col min="2305" max="2305" width="21.875" style="56" customWidth="1"/>
+    <col min="2306" max="2309" width="16.875" style="56" customWidth="1"/>
+    <col min="2310" max="2310" width="17.875" style="56" customWidth="1"/>
+    <col min="2311" max="2311" width="11.5625" style="56" customWidth="1"/>
+    <col min="2312" max="2560" width="8.875" style="56"/>
+    <col min="2561" max="2561" width="21.875" style="56" customWidth="1"/>
+    <col min="2562" max="2565" width="16.875" style="56" customWidth="1"/>
+    <col min="2566" max="2566" width="17.875" style="56" customWidth="1"/>
+    <col min="2567" max="2567" width="11.5625" style="56" customWidth="1"/>
+    <col min="2568" max="2816" width="8.875" style="56"/>
+    <col min="2817" max="2817" width="21.875" style="56" customWidth="1"/>
+    <col min="2818" max="2821" width="16.875" style="56" customWidth="1"/>
+    <col min="2822" max="2822" width="17.875" style="56" customWidth="1"/>
+    <col min="2823" max="2823" width="11.5625" style="56" customWidth="1"/>
+    <col min="2824" max="3072" width="8.875" style="56"/>
+    <col min="3073" max="3073" width="21.875" style="56" customWidth="1"/>
+    <col min="3074" max="3077" width="16.875" style="56" customWidth="1"/>
+    <col min="3078" max="3078" width="17.875" style="56" customWidth="1"/>
+    <col min="3079" max="3079" width="11.5625" style="56" customWidth="1"/>
+    <col min="3080" max="3328" width="8.875" style="56"/>
+    <col min="3329" max="3329" width="21.875" style="56" customWidth="1"/>
+    <col min="3330" max="3333" width="16.875" style="56" customWidth="1"/>
+    <col min="3334" max="3334" width="17.875" style="56" customWidth="1"/>
+    <col min="3335" max="3335" width="11.5625" style="56" customWidth="1"/>
+    <col min="3336" max="3584" width="8.875" style="56"/>
+    <col min="3585" max="3585" width="21.875" style="56" customWidth="1"/>
+    <col min="3586" max="3589" width="16.875" style="56" customWidth="1"/>
+    <col min="3590" max="3590" width="17.875" style="56" customWidth="1"/>
+    <col min="3591" max="3591" width="11.5625" style="56" customWidth="1"/>
+    <col min="3592" max="3840" width="8.875" style="56"/>
+    <col min="3841" max="3841" width="21.875" style="56" customWidth="1"/>
+    <col min="3842" max="3845" width="16.875" style="56" customWidth="1"/>
+    <col min="3846" max="3846" width="17.875" style="56" customWidth="1"/>
+    <col min="3847" max="3847" width="11.5625" style="56" customWidth="1"/>
+    <col min="3848" max="4096" width="8.875" style="56"/>
+    <col min="4097" max="4097" width="21.875" style="56" customWidth="1"/>
+    <col min="4098" max="4101" width="16.875" style="56" customWidth="1"/>
+    <col min="4102" max="4102" width="17.875" style="56" customWidth="1"/>
+    <col min="4103" max="4103" width="11.5625" style="56" customWidth="1"/>
+    <col min="4104" max="4352" width="8.875" style="56"/>
+    <col min="4353" max="4353" width="21.875" style="56" customWidth="1"/>
+    <col min="4354" max="4357" width="16.875" style="56" customWidth="1"/>
+    <col min="4358" max="4358" width="17.875" style="56" customWidth="1"/>
+    <col min="4359" max="4359" width="11.5625" style="56" customWidth="1"/>
+    <col min="4360" max="4608" width="8.875" style="56"/>
+    <col min="4609" max="4609" width="21.875" style="56" customWidth="1"/>
+    <col min="4610" max="4613" width="16.875" style="56" customWidth="1"/>
+    <col min="4614" max="4614" width="17.875" style="56" customWidth="1"/>
+    <col min="4615" max="4615" width="11.5625" style="56" customWidth="1"/>
+    <col min="4616" max="4864" width="8.875" style="56"/>
+    <col min="4865" max="4865" width="21.875" style="56" customWidth="1"/>
+    <col min="4866" max="4869" width="16.875" style="56" customWidth="1"/>
+    <col min="4870" max="4870" width="17.875" style="56" customWidth="1"/>
+    <col min="4871" max="4871" width="11.5625" style="56" customWidth="1"/>
+    <col min="4872" max="5120" width="8.875" style="56"/>
+    <col min="5121" max="5121" width="21.875" style="56" customWidth="1"/>
+    <col min="5122" max="5125" width="16.875" style="56" customWidth="1"/>
+    <col min="5126" max="5126" width="17.875" style="56" customWidth="1"/>
+    <col min="5127" max="5127" width="11.5625" style="56" customWidth="1"/>
+    <col min="5128" max="5376" width="8.875" style="56"/>
+    <col min="5377" max="5377" width="21.875" style="56" customWidth="1"/>
+    <col min="5378" max="5381" width="16.875" style="56" customWidth="1"/>
+    <col min="5382" max="5382" width="17.875" style="56" customWidth="1"/>
+    <col min="5383" max="5383" width="11.5625" style="56" customWidth="1"/>
+    <col min="5384" max="5632" width="8.875" style="56"/>
+    <col min="5633" max="5633" width="21.875" style="56" customWidth="1"/>
+    <col min="5634" max="5637" width="16.875" style="56" customWidth="1"/>
+    <col min="5638" max="5638" width="17.875" style="56" customWidth="1"/>
+    <col min="5639" max="5639" width="11.5625" style="56" customWidth="1"/>
+    <col min="5640" max="5888" width="8.875" style="56"/>
+    <col min="5889" max="5889" width="21.875" style="56" customWidth="1"/>
+    <col min="5890" max="5893" width="16.875" style="56" customWidth="1"/>
+    <col min="5894" max="5894" width="17.875" style="56" customWidth="1"/>
+    <col min="5895" max="5895" width="11.5625" style="56" customWidth="1"/>
+    <col min="5896" max="6144" width="8.875" style="56"/>
+    <col min="6145" max="6145" width="21.875" style="56" customWidth="1"/>
+    <col min="6146" max="6149" width="16.875" style="56" customWidth="1"/>
+    <col min="6150" max="6150" width="17.875" style="56" customWidth="1"/>
+    <col min="6151" max="6151" width="11.5625" style="56" customWidth="1"/>
+    <col min="6152" max="6400" width="8.875" style="56"/>
+    <col min="6401" max="6401" width="21.875" style="56" customWidth="1"/>
+    <col min="6402" max="6405" width="16.875" style="56" customWidth="1"/>
+    <col min="6406" max="6406" width="17.875" style="56" customWidth="1"/>
+    <col min="6407" max="6407" width="11.5625" style="56" customWidth="1"/>
+    <col min="6408" max="6656" width="8.875" style="56"/>
+    <col min="6657" max="6657" width="21.875" style="56" customWidth="1"/>
+    <col min="6658" max="6661" width="16.875" style="56" customWidth="1"/>
+    <col min="6662" max="6662" width="17.875" style="56" customWidth="1"/>
+    <col min="6663" max="6663" width="11.5625" style="56" customWidth="1"/>
+    <col min="6664" max="6912" width="8.875" style="56"/>
+    <col min="6913" max="6913" width="21.875" style="56" customWidth="1"/>
+    <col min="6914" max="6917" width="16.875" style="56" customWidth="1"/>
+    <col min="6918" max="6918" width="17.875" style="56" customWidth="1"/>
+    <col min="6919" max="6919" width="11.5625" style="56" customWidth="1"/>
+    <col min="6920" max="7168" width="8.875" style="56"/>
+    <col min="7169" max="7169" width="21.875" style="56" customWidth="1"/>
+    <col min="7170" max="7173" width="16.875" style="56" customWidth="1"/>
+    <col min="7174" max="7174" width="17.875" style="56" customWidth="1"/>
+    <col min="7175" max="7175" width="11.5625" style="56" customWidth="1"/>
+    <col min="7176" max="7424" width="8.875" style="56"/>
+    <col min="7425" max="7425" width="21.875" style="56" customWidth="1"/>
+    <col min="7426" max="7429" width="16.875" style="56" customWidth="1"/>
+    <col min="7430" max="7430" width="17.875" style="56" customWidth="1"/>
+    <col min="7431" max="7431" width="11.5625" style="56" customWidth="1"/>
+    <col min="7432" max="7680" width="8.875" style="56"/>
+    <col min="7681" max="7681" width="21.875" style="56" customWidth="1"/>
+    <col min="7682" max="7685" width="16.875" style="56" customWidth="1"/>
+    <col min="7686" max="7686" width="17.875" style="56" customWidth="1"/>
+    <col min="7687" max="7687" width="11.5625" style="56" customWidth="1"/>
+    <col min="7688" max="7936" width="8.875" style="56"/>
+    <col min="7937" max="7937" width="21.875" style="56" customWidth="1"/>
+    <col min="7938" max="7941" width="16.875" style="56" customWidth="1"/>
+    <col min="7942" max="7942" width="17.875" style="56" customWidth="1"/>
+    <col min="7943" max="7943" width="11.5625" style="56" customWidth="1"/>
+    <col min="7944" max="8192" width="8.875" style="56"/>
+    <col min="8193" max="8193" width="21.875" style="56" customWidth="1"/>
+    <col min="8194" max="8197" width="16.875" style="56" customWidth="1"/>
+    <col min="8198" max="8198" width="17.875" style="56" customWidth="1"/>
+    <col min="8199" max="8199" width="11.5625" style="56" customWidth="1"/>
+    <col min="8200" max="8448" width="8.875" style="56"/>
+    <col min="8449" max="8449" width="21.875" style="56" customWidth="1"/>
+    <col min="8450" max="8453" width="16.875" style="56" customWidth="1"/>
+    <col min="8454" max="8454" width="17.875" style="56" customWidth="1"/>
+    <col min="8455" max="8455" width="11.5625" style="56" customWidth="1"/>
+    <col min="8456" max="8704" width="8.875" style="56"/>
+    <col min="8705" max="8705" width="21.875" style="56" customWidth="1"/>
+    <col min="8706" max="8709" width="16.875" style="56" customWidth="1"/>
+    <col min="8710" max="8710" width="17.875" style="56" customWidth="1"/>
+    <col min="8711" max="8711" width="11.5625" style="56" customWidth="1"/>
+    <col min="8712" max="8960" width="8.875" style="56"/>
+    <col min="8961" max="8961" width="21.875" style="56" customWidth="1"/>
+    <col min="8962" max="8965" width="16.875" style="56" customWidth="1"/>
+    <col min="8966" max="8966" width="17.875" style="56" customWidth="1"/>
+    <col min="8967" max="8967" width="11.5625" style="56" customWidth="1"/>
+    <col min="8968" max="9216" width="8.875" style="56"/>
+    <col min="9217" max="9217" width="21.875" style="56" customWidth="1"/>
+    <col min="9218" max="9221" width="16.875" style="56" customWidth="1"/>
+    <col min="9222" max="9222" width="17.875" style="56" customWidth="1"/>
+    <col min="9223" max="9223" width="11.5625" style="56" customWidth="1"/>
+    <col min="9224" max="9472" width="8.875" style="56"/>
+    <col min="9473" max="9473" width="21.875" style="56" customWidth="1"/>
+    <col min="9474" max="9477" width="16.875" style="56" customWidth="1"/>
+    <col min="9478" max="9478" width="17.875" style="56" customWidth="1"/>
+    <col min="9479" max="9479" width="11.5625" style="56" customWidth="1"/>
+    <col min="9480" max="9728" width="8.875" style="56"/>
+    <col min="9729" max="9729" width="21.875" style="56" customWidth="1"/>
+    <col min="9730" max="9733" width="16.875" style="56" customWidth="1"/>
+    <col min="9734" max="9734" width="17.875" style="56" customWidth="1"/>
+    <col min="9735" max="9735" width="11.5625" style="56" customWidth="1"/>
+    <col min="9736" max="9984" width="8.875" style="56"/>
+    <col min="9985" max="9985" width="21.875" style="56" customWidth="1"/>
+    <col min="9986" max="9989" width="16.875" style="56" customWidth="1"/>
+    <col min="9990" max="9990" width="17.875" style="56" customWidth="1"/>
+    <col min="9991" max="9991" width="11.5625" style="56" customWidth="1"/>
+    <col min="9992" max="10240" width="8.875" style="56"/>
+    <col min="10241" max="10241" width="21.875" style="56" customWidth="1"/>
+    <col min="10242" max="10245" width="16.875" style="56" customWidth="1"/>
+    <col min="10246" max="10246" width="17.875" style="56" customWidth="1"/>
+    <col min="10247" max="10247" width="11.5625" style="56" customWidth="1"/>
+    <col min="10248" max="10496" width="8.875" style="56"/>
+    <col min="10497" max="10497" width="21.875" style="56" customWidth="1"/>
+    <col min="10498" max="10501" width="16.875" style="56" customWidth="1"/>
+    <col min="10502" max="10502" width="17.875" style="56" customWidth="1"/>
+    <col min="10503" max="10503" width="11.5625" style="56" customWidth="1"/>
+    <col min="10504" max="10752" width="8.875" style="56"/>
+    <col min="10753" max="10753" width="21.875" style="56" customWidth="1"/>
+    <col min="10754" max="10757" width="16.875" style="56" customWidth="1"/>
+    <col min="10758" max="10758" width="17.875" style="56" customWidth="1"/>
+    <col min="10759" max="10759" width="11.5625" style="56" customWidth="1"/>
+    <col min="10760" max="11008" width="8.875" style="56"/>
+    <col min="11009" max="11009" width="21.875" style="56" customWidth="1"/>
+    <col min="11010" max="11013" width="16.875" style="56" customWidth="1"/>
+    <col min="11014" max="11014" width="17.875" style="56" customWidth="1"/>
+    <col min="11015" max="11015" width="11.5625" style="56" customWidth="1"/>
+    <col min="11016" max="11264" width="8.875" style="56"/>
+    <col min="11265" max="11265" width="21.875" style="56" customWidth="1"/>
+    <col min="11266" max="11269" width="16.875" style="56" customWidth="1"/>
+    <col min="11270" max="11270" width="17.875" style="56" customWidth="1"/>
+    <col min="11271" max="11271" width="11.5625" style="56" customWidth="1"/>
+    <col min="11272" max="11520" width="8.875" style="56"/>
+    <col min="11521" max="11521" width="21.875" style="56" customWidth="1"/>
+    <col min="11522" max="11525" width="16.875" style="56" customWidth="1"/>
+    <col min="11526" max="11526" width="17.875" style="56" customWidth="1"/>
+    <col min="11527" max="11527" width="11.5625" style="56" customWidth="1"/>
+    <col min="11528" max="11776" width="8.875" style="56"/>
+    <col min="11777" max="11777" width="21.875" style="56" customWidth="1"/>
+    <col min="11778" max="11781" width="16.875" style="56" customWidth="1"/>
+    <col min="11782" max="11782" width="17.875" style="56" customWidth="1"/>
+    <col min="11783" max="11783" width="11.5625" style="56" customWidth="1"/>
+    <col min="11784" max="12032" width="8.875" style="56"/>
+    <col min="12033" max="12033" width="21.875" style="56" customWidth="1"/>
+    <col min="12034" max="12037" width="16.875" style="56" customWidth="1"/>
+    <col min="12038" max="12038" width="17.875" style="56" customWidth="1"/>
+    <col min="12039" max="12039" width="11.5625" style="56" customWidth="1"/>
+    <col min="12040" max="12288" width="8.875" style="56"/>
+    <col min="12289" max="12289" width="21.875" style="56" customWidth="1"/>
+    <col min="12290" max="12293" width="16.875" style="56" customWidth="1"/>
+    <col min="12294" max="12294" width="17.875" style="56" customWidth="1"/>
+    <col min="12295" max="12295" width="11.5625" style="56" customWidth="1"/>
+    <col min="12296" max="12544" width="8.875" style="56"/>
+    <col min="12545" max="12545" width="21.875" style="56" customWidth="1"/>
+    <col min="12546" max="12549" width="16.875" style="56" customWidth="1"/>
+    <col min="12550" max="12550" width="17.875" style="56" customWidth="1"/>
+    <col min="12551" max="12551" width="11.5625" style="56" customWidth="1"/>
+    <col min="12552" max="12800" width="8.875" style="56"/>
+    <col min="12801" max="12801" width="21.875" style="56" customWidth="1"/>
+    <col min="12802" max="12805" width="16.875" style="56" customWidth="1"/>
+    <col min="12806" max="12806" width="17.875" style="56" customWidth="1"/>
+    <col min="12807" max="12807" width="11.5625" style="56" customWidth="1"/>
+    <col min="12808" max="13056" width="8.875" style="56"/>
+    <col min="13057" max="13057" width="21.875" style="56" customWidth="1"/>
+    <col min="13058" max="13061" width="16.875" style="56" customWidth="1"/>
+    <col min="13062" max="13062" width="17.875" style="56" customWidth="1"/>
+    <col min="13063" max="13063" width="11.5625" style="56" customWidth="1"/>
+    <col min="13064" max="13312" width="8.875" style="56"/>
+    <col min="13313" max="13313" width="21.875" style="56" customWidth="1"/>
+    <col min="13314" max="13317" width="16.875" style="56" customWidth="1"/>
+    <col min="13318" max="13318" width="17.875" style="56" customWidth="1"/>
+    <col min="13319" max="13319" width="11.5625" style="56" customWidth="1"/>
+    <col min="13320" max="13568" width="8.875" style="56"/>
+    <col min="13569" max="13569" width="21.875" style="56" customWidth="1"/>
+    <col min="13570" max="13573" width="16.875" style="56" customWidth="1"/>
+    <col min="13574" max="13574" width="17.875" style="56" customWidth="1"/>
+    <col min="13575" max="13575" width="11.5625" style="56" customWidth="1"/>
+    <col min="13576" max="13824" width="8.875" style="56"/>
+    <col min="13825" max="13825" width="21.875" style="56" customWidth="1"/>
+    <col min="13826" max="13829" width="16.875" style="56" customWidth="1"/>
+    <col min="13830" max="13830" width="17.875" style="56" customWidth="1"/>
+    <col min="13831" max="13831" width="11.5625" style="56" customWidth="1"/>
+    <col min="13832" max="14080" width="8.875" style="56"/>
+    <col min="14081" max="14081" width="21.875" style="56" customWidth="1"/>
+    <col min="14082" max="14085" width="16.875" style="56" customWidth="1"/>
+    <col min="14086" max="14086" width="17.875" style="56" customWidth="1"/>
+    <col min="14087" max="14087" width="11.5625" style="56" customWidth="1"/>
+    <col min="14088" max="14336" width="8.875" style="56"/>
+    <col min="14337" max="14337" width="21.875" style="56" customWidth="1"/>
+    <col min="14338" max="14341" width="16.875" style="56" customWidth="1"/>
+    <col min="14342" max="14342" width="17.875" style="56" customWidth="1"/>
+    <col min="14343" max="14343" width="11.5625" style="56" customWidth="1"/>
+    <col min="14344" max="14592" width="8.875" style="56"/>
+    <col min="14593" max="14593" width="21.875" style="56" customWidth="1"/>
+    <col min="14594" max="14597" width="16.875" style="56" customWidth="1"/>
+    <col min="14598" max="14598" width="17.875" style="56" customWidth="1"/>
+    <col min="14599" max="14599" width="11.5625" style="56" customWidth="1"/>
+    <col min="14600" max="14848" width="8.875" style="56"/>
+    <col min="14849" max="14849" width="21.875" style="56" customWidth="1"/>
+    <col min="14850" max="14853" width="16.875" style="56" customWidth="1"/>
+    <col min="14854" max="14854" width="17.875" style="56" customWidth="1"/>
+    <col min="14855" max="14855" width="11.5625" style="56" customWidth="1"/>
+    <col min="14856" max="15104" width="8.875" style="56"/>
+    <col min="15105" max="15105" width="21.875" style="56" customWidth="1"/>
+    <col min="15106" max="15109" width="16.875" style="56" customWidth="1"/>
+    <col min="15110" max="15110" width="17.875" style="56" customWidth="1"/>
+    <col min="15111" max="15111" width="11.5625" style="56" customWidth="1"/>
+    <col min="15112" max="15360" width="8.875" style="56"/>
+    <col min="15361" max="15361" width="21.875" style="56" customWidth="1"/>
+    <col min="15362" max="15365" width="16.875" style="56" customWidth="1"/>
+    <col min="15366" max="15366" width="17.875" style="56" customWidth="1"/>
+    <col min="15367" max="15367" width="11.5625" style="56" customWidth="1"/>
+    <col min="15368" max="15616" width="8.875" style="56"/>
+    <col min="15617" max="15617" width="21.875" style="56" customWidth="1"/>
+    <col min="15618" max="15621" width="16.875" style="56" customWidth="1"/>
+    <col min="15622" max="15622" width="17.875" style="56" customWidth="1"/>
+    <col min="15623" max="15623" width="11.5625" style="56" customWidth="1"/>
+    <col min="15624" max="15872" width="8.875" style="56"/>
+    <col min="15873" max="15873" width="21.875" style="56" customWidth="1"/>
+    <col min="15874" max="15877" width="16.875" style="56" customWidth="1"/>
+    <col min="15878" max="15878" width="17.875" style="56" customWidth="1"/>
+    <col min="15879" max="15879" width="11.5625" style="56" customWidth="1"/>
+    <col min="15880" max="16128" width="8.875" style="56"/>
+    <col min="16129" max="16129" width="21.875" style="56" customWidth="1"/>
+    <col min="16130" max="16133" width="16.875" style="56" customWidth="1"/>
+    <col min="16134" max="16134" width="17.875" style="56" customWidth="1"/>
+    <col min="16135" max="16135" width="11.5625" style="56" customWidth="1"/>
+    <col min="16136" max="16384" width="8.875" style="56"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="59"/>
+      <c r="H1" s="57"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="H2" s="59"/>
+      <c r="H2" s="57"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="58" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="61" t="s">
+      <c r="C4" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D4" s="61" t="s">
+      <c r="D4" s="59" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="58" t="s">
+      <c r="A5" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="B5" s="62">
+      <c r="B5" s="60">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C5" s="62">
+      <c r="C5" s="60">
         <v>0.11</v>
       </c>
-      <c r="D5" s="62">
+      <c r="D5" s="60">
         <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="56" t="s">
         <v>163</v>
       </c>
-      <c r="B6" s="62">
+      <c r="B6" s="60">
         <v>0.2</v>
       </c>
-      <c r="C6" s="62">
+      <c r="C6" s="60">
         <v>0.15</v>
       </c>
-      <c r="D6" s="62">
+      <c r="D6" s="60">
         <v>0.08</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="58" t="s">
+      <c r="A8" s="56" t="s">
         <v>164</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D8" s="61" t="s">
+      <c r="D8" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="G8" s="61" t="s">
+      <c r="G8" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="H8" s="61" t="s">
+      <c r="H8" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="I8" s="61" t="s">
+      <c r="I8" s="59" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="B9" s="62">
+      <c r="B9" s="60">
         <v>1</v>
       </c>
-      <c r="C9" s="62">
+      <c r="C9" s="60">
         <v>0.6</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="60">
         <v>0.4</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="G9" s="63"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="65"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="63"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="56" t="s">
         <v>160</v>
       </c>
-      <c r="B10" s="62">
+      <c r="B10" s="60">
         <v>0.6</v>
       </c>
-      <c r="C10" s="62">
+      <c r="C10" s="60">
         <v>1</v>
       </c>
-      <c r="D10" s="62">
+      <c r="D10" s="60">
         <v>0.7</v>
       </c>
-      <c r="F10" s="58" t="s">
+      <c r="F10" s="56" t="s">
         <v>160</v>
       </c>
-      <c r="G10" s="66"/>
-      <c r="I10" s="67"/>
+      <c r="G10" s="64"/>
+      <c r="I10" s="65"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="B11" s="62">
+      <c r="B11" s="60">
         <v>0.4</v>
       </c>
-      <c r="C11" s="62">
+      <c r="C11" s="60">
         <v>0.7</v>
       </c>
-      <c r="D11" s="62">
+      <c r="D11" s="60">
         <v>1</v>
       </c>
-      <c r="F11" s="58" t="s">
+      <c r="F11" s="56" t="s">
         <v>161</v>
       </c>
-      <c r="G11" s="68"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="70"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="68"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="69" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B14" s="61" t="s">
+      <c r="B14" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="61" t="s">
+      <c r="C14" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="61" t="s">
+      <c r="D14" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="E14" s="72"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="72"/>
+      <c r="E14" s="70"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="70"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="73" t="s">
+      <c r="A15" s="71" t="s">
         <v>167</v>
       </c>
-      <c r="B15" s="74"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
-      <c r="F15" s="73"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="F15" s="71"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="F16" s="75"/>
+      <c r="F16" s="73"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="71" t="s">
+      <c r="A17" s="69" t="s">
         <v>168</v>
       </c>
-      <c r="F17" s="75"/>
+      <c r="F17" s="73"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B18" s="72" t="s">
+      <c r="B18" s="70" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72" t="s">
+      <c r="C18" s="70"/>
+      <c r="D18" s="70" t="s">
         <v>170</v>
       </c>
-      <c r="F18" s="75"/>
+      <c r="F18" s="73"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B19" s="76"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="78"/>
-      <c r="F19" s="75"/>
+      <c r="B19" s="74"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="76"/>
+      <c r="F19" s="73"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F20" s="75"/>
+      <c r="F20" s="73"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="55" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B22" s="72" t="s">
+      <c r="B22" s="70" t="s">
         <v>172</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72" t="s">
+      <c r="C22" s="70"/>
+      <c r="D22" s="70" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B23" s="76"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="80">
+      <c r="B23" s="74"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="78">
         <v>0.12</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="71" t="s">
+      <c r="A25" s="69" t="s">
         <v>174</v>
       </c>
-      <c r="B25" s="81"/>
+      <c r="B25" s="79"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="58" t="s">
+      <c r="A26" s="56" t="s">
         <v>175</v>
       </c>
-      <c r="B26" s="81"/>
+      <c r="B26" s="79"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="71"/>
+      <c r="A28" s="69"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6137,10 +6119,10 @@
       <c r="A2" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="41">
+      <c r="B2" s="39">
         <v>330.32553318164355</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2" s="39">
         <v>923.75928147692673</v>
       </c>
       <c r="K2">
@@ -6155,10 +6137,10 @@
       <c r="B3">
         <v>80</v>
       </c>
-      <c r="C3" s="83">
+      <c r="C3" s="81">
         <v>129</v>
       </c>
-      <c r="D3" s="96">
+      <c r="D3" s="87">
         <f>SUMPRODUCT($B$2:$C$2,B3:C3)</f>
         <v>145590.98996505502</v>
       </c>
@@ -6185,14 +6167,14 @@
         <f>_xlfn.NORM.S.INV(0.9)*SQRT(SUMPRODUCT(B10:C10,B11:C11))</f>
         <v>2805.8243247005807</v>
       </c>
-      <c r="F4" s="95">
+      <c r="F4" s="86">
         <f>D4+E4</f>
         <v>10000.007679470358</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="H4" s="86">
+      <c r="H4" s="84">
         <v>10000</v>
       </c>
     </row>
@@ -6210,14 +6192,14 @@
         <f t="shared" si="0"/>
         <v>2177.8440961354972</v>
       </c>
-      <c r="F5" s="95">
+      <c r="F5" s="86">
         <f>D5+E5</f>
         <v>2177.8440961354972</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="86">
+      <c r="H5" s="84">
         <v>3000</v>
       </c>
     </row>
@@ -6521,20 +6503,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="87" t="s">
+      <c r="C1" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C2" s="87" t="s">
+      <c r="C2" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
@@ -6546,7 +6528,7 @@
       <c r="E3" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="87" t="s">
+      <c r="F3" s="88" t="s">
         <v>33</v>
       </c>
     </row>
@@ -6560,10 +6542,10 @@
       <c r="E4" t="s">
         <v>94</v>
       </c>
-      <c r="F4" s="87"/>
+      <c r="F4" s="88"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="87"/>
+      <c r="A5" s="88"/>
       <c r="B5" t="s">
         <v>97</v>
       </c>
@@ -6579,7 +6561,7 @@
       <c r="F5" s="13"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="87"/>
+      <c r="A6" s="88"/>
       <c r="B6" t="s">
         <v>98</v>
       </c>
@@ -6595,7 +6577,7 @@
       <c r="F6" s="13"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="87"/>
+      <c r="A7" s="88"/>
       <c r="B7" t="s">
         <v>99</v>
       </c>
@@ -6611,10 +6593,10 @@
       <c r="F7" s="13"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="87" t="s">
+      <c r="A9" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="87"/>
+      <c r="B9" s="88"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
@@ -6971,21 +6953,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005D21A9346877C94FBE0D2EF98A54C8DF" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b9d30dfdbb3c728c42ac273b0b267a13">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0f411969-aaa6-47b2-a14e-e9510c0df77f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ca649492ee4635bde6ac1a281be3e98b" ns2:_="">
     <xsd:import namespace="0f411969-aaa6-47b2-a14e-e9510c0df77f"/>
@@ -7123,24 +7090,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{045A6F27-BBFE-48F3-BE55-9FF8155F59CF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4499BA0A-D035-4121-AEC6-666388DF038D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7471329D-8B35-4081-B86A-5ED8B1A94B51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7156,4 +7121,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4499BA0A-D035-4121-AEC6-666388DF038D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{045A6F27-BBFE-48F3-BE55-9FF8155F59CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>